--- a/outputs/metadados_piloto.xlsx
+++ b/outputs/metadados_piloto.xlsx
@@ -16,20 +16,20 @@
     <sheet name="Arquivos gerados" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resumo!$A$3:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="750">
   <si>
     <t>campo</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Piloto computacional de mobilidade urbana, diferenciação socioespacial e entropia socioeconômica de trajetórias</t>
   </si>
   <si>
-    <t>2026-09-28T07:19:24.330882+00:00</t>
+    <t>2026-09-28T07:41:40.727776+00:00</t>
   </si>
   <si>
     <t>português</t>
@@ -298,6 +298,33 @@
     <t>shape_segment_distance_m</t>
   </si>
   <si>
+    <t>access_walk_distance_m</t>
+  </si>
+  <si>
+    <t>access_walk_time_s</t>
+  </si>
+  <si>
+    <t>initial_wait_time_s</t>
+  </si>
+  <si>
+    <t>transfer_and_dwell_time_s</t>
+  </si>
+  <si>
+    <t>n_boardings</t>
+  </si>
+  <si>
+    <t>n_transfers</t>
+  </si>
+  <si>
+    <t>mean_in_vehicle_time_per_connection_s</t>
+  </si>
+  <si>
+    <t>egress_walk_distance_m</t>
+  </si>
+  <si>
+    <t>egress_walk_time_s</t>
+  </si>
+  <si>
     <t>agente</t>
   </si>
   <si>
@@ -334,6 +361,12 @@
     <t>transporte coletivo</t>
   </si>
   <si>
+    <t>roteamento de transporte coletivo</t>
+  </si>
+  <si>
+    <t>diagnóstico de transporte coletivo</t>
+  </si>
+  <si>
     <t>identificador</t>
   </si>
   <si>
@@ -409,6 +442,15 @@
     <t>m ao longo do shape</t>
   </si>
   <si>
+    <t>embarques</t>
+  </si>
+  <si>
+    <t>transferências</t>
+  </si>
+  <si>
+    <t>s/conexão</t>
+  </si>
+  <si>
     <t>Identificador único do agente sintético</t>
   </si>
   <si>
@@ -616,6 +658,36 @@
     <t>Distância ao longo do shape entre duas paradas consecutivas quando a projeção geométrica é válida</t>
   </si>
   <si>
+    <t>Distância total percorrida a pé entre a origem e a parada de embarque</t>
+  </si>
+  <si>
+    <t>Tempo total de caminhada entre a origem e a parada de embarque</t>
+  </si>
+  <si>
+    <t>Tempo entre a chegada à parada de embarque e a partida do primeiro ônibus</t>
+  </si>
+  <si>
+    <t>Soma do tempo programado dentro dos veículos usados na viagem</t>
+  </si>
+  <si>
+    <t>Tempo acumulado entre conexões que não corresponde ao deslocamento dentro do veículo</t>
+  </si>
+  <si>
+    <t>Quantidade de viagens GTFS distintas embarcadas ao longo do itinerário</t>
+  </si>
+  <si>
+    <t>Quantidade de trocas de viagem GTFS ao longo do itinerário</t>
+  </si>
+  <si>
+    <t>Tempo médio dentro do veículo por conexão GTFS usada na rota, empregado como diagnóstico de qualidade temporal</t>
+  </si>
+  <si>
+    <t>Distância total percorrida a pé entre a parada de desembarque e o destino</t>
+  </si>
+  <si>
+    <t>Tempo total de caminhada entre a parada de desembarque e o destino</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Variáveis</t>
   </si>
   <si>
@@ -655,6 +727,27 @@
     <t>transit.network.service_date_strategy</t>
   </si>
   <si>
+    <t>transit.routing.max_access_walk_m</t>
+  </si>
+  <si>
+    <t>transit.routing.max_egress_walk_m</t>
+  </si>
+  <si>
+    <t>transit.routing.minimum_transfer_time_s</t>
+  </si>
+  <si>
+    <t>transit.routing.max_total_travel_time_s</t>
+  </si>
+  <si>
+    <t>transit.routing.diagnostics.sample_size</t>
+  </si>
+  <si>
+    <t>transit.routing.diagnostics.departure_time_s</t>
+  </si>
+  <si>
+    <t>transit.routing.diagnostics.seed</t>
+  </si>
+  <si>
     <t>income.groups.low.share</t>
   </si>
   <si>
@@ -859,6 +952,9 @@
     <t>m/s</t>
   </si>
   <si>
+    <t>viagens OD</t>
+  </si>
+  <si>
     <t>moeda da variável de renda de origem</t>
   </si>
   <si>
@@ -904,6 +1000,27 @@
     <t>Regra usada para selecionar uma data de serviço representativa do feed</t>
   </si>
   <si>
+    <t>Distância máxima de caminhada entre a origem e uma parada candidata de embarque</t>
+  </si>
+  <si>
+    <t>Distância máxima de caminhada entre uma parada candidata de desembarque e o destino</t>
+  </si>
+  <si>
+    <t>Tempo mínimo provisório exigido para realizar transferência entre viagens na mesma parada</t>
+  </si>
+  <si>
+    <t>Horizonte máximo provisório considerado em uma consulta de transporte coletivo</t>
+  </si>
+  <si>
+    <t>Quantidade de pares origem-destino usada no diagnóstico técnico do roteador temporal</t>
+  </si>
+  <si>
+    <t>Horário de partida comum usado nas consultas do diagnóstico técnico</t>
+  </si>
+  <si>
+    <t>Semente pseudoaleatória usada para selecionar os pares origem-destino do diagnóstico</t>
+  </si>
+  <si>
     <t>Participação populacional configurada para o grupo de renda low</t>
   </si>
   <si>
@@ -1165,6 +1282,21 @@
     <t>Perfil diário de oferta GTFS</t>
   </si>
   <si>
+    <t>Roteamento temporal por varredura de conexões</t>
+  </si>
+  <si>
+    <t>Busca de paradas acessíveis pela rede de caminhada</t>
+  </si>
+  <si>
+    <t>Transferência entre viagens no mesmo stop_id</t>
+  </si>
+  <si>
+    <t>Diagnóstico amostral do roteamento temporal</t>
+  </si>
+  <si>
+    <t>Validação de continuidade do itinerário de transporte coletivo</t>
+  </si>
+  <si>
     <t>generate_population</t>
   </si>
   <si>
@@ -1222,6 +1354,15 @@
     <t>_build_service_day_profile</t>
   </si>
   <si>
+    <t>TransitRouter.route</t>
+  </si>
+  <si>
+    <t>TransitRouter._candidate_stops</t>
+  </si>
+  <si>
+    <t>run_diagnostics</t>
+  </si>
+  <si>
     <t>Gera agentes sintéticos preservando as participações configuradas para os grupos de renda</t>
   </si>
   <si>
@@ -1291,6 +1432,21 @@
     <t>Calcula o número de viagens programadas por data e identifica uma data de referência pela maior oferta do feed</t>
   </si>
   <si>
+    <t>Procura a chegada mais cedo percorrendo as conexões GTFS em ordem temporal e combinando acesso e egresso pela rede de caminhada</t>
+  </si>
+  <si>
+    <t>Usa Dijkstra limitado por distância para identificar múltiplas paradas alcançáveis a partir da origem ou do destino</t>
+  </si>
+  <si>
+    <t>Permite a troca entre viagens GTFS na mesma parada quando o intervalo disponível atende ao tempo mínimo de transferência configurado</t>
+  </si>
+  <si>
+    <t>Seleciona pares origem-destino reprodutíveis das bases do piloto e resume cobertura, tempos, caminhada de acesso e egresso e transferências</t>
+  </si>
+  <si>
+    <t>Exige continuidade entre a parada de destino de uma conexão e a parada de origem da conexão seguinte e preserva a ordem numérica de stop_sequence em empates temporais</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Métodos de análise</t>
   </si>
   <si>
@@ -1339,6 +1495,12 @@
     <t>Qualidade média de harmonização</t>
   </si>
   <si>
+    <t>Contagem de conexões com duração zero</t>
+  </si>
+  <si>
+    <t>Tempo médio por conexão veicular</t>
+  </si>
+  <si>
     <t>Quantifica agentes, viagens, arestas, segmentos, paradas, rotas, shapes e demais unidades discretas</t>
   </si>
   <si>
@@ -1384,6 +1546,12 @@
     <t>Resume a qualidade das correspondências geométricas entre arestas modais e segmentos físicos</t>
   </si>
   <si>
+    <t>Quantifica conexões GTFS cujo tempo entre partida e chegada é igual a zero para diagnosticar limitações do preenchimento temporal</t>
+  </si>
+  <si>
+    <t>Divide o tempo dentro do veículo pelo número de conexões GTFS usadas na rota para identificar itinerários temporalmente suspeitos</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Estatísticas</t>
   </si>
   <si>
@@ -1441,6 +1609,12 @@
     <t>Deduplicação agente × segmento</t>
   </si>
   <si>
+    <t>Ordenação numérica de stop_sequence em empates temporais</t>
+  </si>
+  <si>
+    <t>Validação de continuidade entre conexões GTFS</t>
+  </si>
+  <si>
     <t>Remove espaços excedentes e normaliza campos textuais usados como identificadores e categorias</t>
   </si>
   <si>
@@ -1495,6 +1669,12 @@
     <t>Usa apenas uma observação por agente e segmento para composição socioeconômica e evita inflar pesos por repetição de passagem</t>
   </si>
   <si>
+    <t>Ordena conexões com o mesmo horário usando a sequência numérica da parada e evita a ordenação lexicográfica de identificadores como 19 antes de 2</t>
+  </si>
+  <si>
+    <t>Confere se cada conexão do itinerário começa na parada onde a conexão anterior terminou antes de aceitar o resultado do roteamento</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Métodos de limpeza</t>
   </si>
   <si>
@@ -1687,6 +1867,9 @@
     <t>map_manifest.csv</t>
   </si>
   <si>
+    <t>transit_routing_diagnostics.csv</t>
+  </si>
+  <si>
     <t>metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -1867,6 +2050,9 @@
     <t>outputs/pilot/maps/map_manifest.csv</t>
   </si>
   <si>
+    <t>outputs/pilot/transit_routing_diagnostics.csv</t>
+  </si>
+  <si>
     <t>outputs/metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -2075,6 +2261,9 @@
   </si>
   <si>
     <t>Manifesto dos mapas gerados com identificação, quantidade de segmentos e descrição em português</t>
+  </si>
+  <si>
+    <t>Amostra de consultas origem-destino usada para validar cobertura, tempos, acesso, egresso e transferências do roteador temporal de ônibus</t>
   </si>
   <si>
     <t>Planilha consolidada com variáveis, parâmetros, métodos, estatísticas, limpeza e arquivos do piloto</t>
@@ -2555,7 +2744,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
@@ -2563,7 +2752,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
@@ -2571,7 +2760,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
@@ -2579,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
@@ -2587,7 +2776,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2601,7 +2790,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2612,7 +2801,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2637,13 +2826,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
@@ -2651,13 +2840,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
@@ -2665,13 +2854,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
@@ -2679,13 +2868,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
@@ -2693,13 +2882,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
@@ -2707,13 +2896,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="34" customHeight="1">
@@ -2721,13 +2910,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34" customHeight="1">
@@ -2735,13 +2924,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1">
@@ -2749,13 +2938,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34" customHeight="1">
@@ -2763,13 +2952,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34" customHeight="1">
@@ -2777,13 +2966,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="34" customHeight="1">
@@ -2791,13 +2980,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34" customHeight="1">
@@ -2805,13 +2994,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="34" customHeight="1">
@@ -2819,13 +3008,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34" customHeight="1">
@@ -2833,13 +3022,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="34" customHeight="1">
@@ -2847,13 +3036,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="34" customHeight="1">
@@ -2861,13 +3050,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" customHeight="1">
@@ -2875,13 +3064,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" customHeight="1">
@@ -2889,13 +3078,13 @@
         <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" customHeight="1">
@@ -2903,13 +3092,13 @@
         <v>39</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" customHeight="1">
@@ -2917,13 +3106,13 @@
         <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="34" customHeight="1">
@@ -2931,13 +3120,13 @@
         <v>41</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="34" customHeight="1">
@@ -2945,13 +3134,13 @@
         <v>42</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="34" customHeight="1">
@@ -2959,13 +3148,13 @@
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="34" customHeight="1">
@@ -2973,13 +3162,13 @@
         <v>44</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="34" customHeight="1">
@@ -2987,13 +3176,13 @@
         <v>45</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="34" customHeight="1">
@@ -3001,13 +3190,13 @@
         <v>46</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="34" customHeight="1">
@@ -3015,13 +3204,13 @@
         <v>47</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="34" customHeight="1">
@@ -3029,13 +3218,13 @@
         <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="34" customHeight="1">
@@ -3043,13 +3232,13 @@
         <v>49</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="34" customHeight="1">
@@ -3057,13 +3246,13 @@
         <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="34" customHeight="1">
@@ -3071,13 +3260,13 @@
         <v>51</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="34" customHeight="1">
@@ -3085,13 +3274,13 @@
         <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="34" customHeight="1">
@@ -3099,13 +3288,13 @@
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" customHeight="1">
@@ -3113,13 +3302,13 @@
         <v>54</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="34" customHeight="1">
@@ -3127,13 +3316,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="34" customHeight="1">
@@ -3141,13 +3330,13 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="34" customHeight="1">
@@ -3155,13 +3344,13 @@
         <v>57</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="34" customHeight="1">
@@ -3169,13 +3358,13 @@
         <v>58</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" customHeight="1">
@@ -3183,13 +3372,13 @@
         <v>59</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="34" customHeight="1">
@@ -3197,13 +3386,13 @@
         <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="34" customHeight="1">
@@ -3211,13 +3400,13 @@
         <v>61</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="34" customHeight="1">
@@ -3225,13 +3414,13 @@
         <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="34" customHeight="1">
@@ -3239,13 +3428,13 @@
         <v>63</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="34" customHeight="1">
@@ -3253,13 +3442,13 @@
         <v>64</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="34" customHeight="1">
@@ -3267,13 +3456,13 @@
         <v>65</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="34" customHeight="1">
@@ -3281,13 +3470,13 @@
         <v>66</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="34" customHeight="1">
@@ -3295,13 +3484,13 @@
         <v>67</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="34" customHeight="1">
@@ -3309,13 +3498,13 @@
         <v>68</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="34" customHeight="1">
@@ -3323,13 +3512,13 @@
         <v>69</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="34" customHeight="1">
@@ -3337,13 +3526,13 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="34" customHeight="1">
@@ -3351,13 +3540,13 @@
         <v>71</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="34" customHeight="1">
@@ -3365,13 +3554,13 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="34" customHeight="1">
@@ -3379,13 +3568,13 @@
         <v>73</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="34" customHeight="1">
@@ -3393,13 +3582,13 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="34" customHeight="1">
@@ -3407,13 +3596,13 @@
         <v>75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="34" customHeight="1">
@@ -3421,13 +3610,13 @@
         <v>76</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="34" customHeight="1">
@@ -3435,13 +3624,13 @@
         <v>77</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="34" customHeight="1">
@@ -3449,13 +3638,13 @@
         <v>78</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="34" customHeight="1">
@@ -3463,13 +3652,13 @@
         <v>79</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="34" customHeight="1">
@@ -3477,13 +3666,13 @@
         <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="34" customHeight="1">
@@ -3491,13 +3680,13 @@
         <v>81</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="34" customHeight="1">
@@ -3505,13 +3694,13 @@
         <v>82</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="34" customHeight="1">
@@ -3519,13 +3708,13 @@
         <v>83</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="34" customHeight="1">
@@ -3533,13 +3722,13 @@
         <v>84</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="34" customHeight="1">
@@ -3547,13 +3736,13 @@
         <v>85</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="34" customHeight="1">
@@ -3561,13 +3750,13 @@
         <v>86</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="34" customHeight="1">
@@ -3575,13 +3764,13 @@
         <v>87</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="34" customHeight="1">
@@ -3589,17 +3778,157 @@
         <v>88</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>194</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="34" customHeight="1">
+      <c r="A73" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="34" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="34" customHeight="1">
+      <c r="A75" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="34" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="34" customHeight="1">
+      <c r="A77" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="34" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="34" customHeight="1">
+      <c r="A79" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="34" customHeight="1">
+      <c r="A80" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="34" customHeight="1">
+      <c r="A81" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="34" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D72"/>
+  <autoFilter ref="A3:D82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3609,7 +3938,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.7109375" customWidth="1"/>
@@ -3621,7 +3950,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3642,1193 +3971,1312 @@
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="B4" s="3">
         <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="B5" s="4">
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="B7" s="4">
         <v>30000</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="B9" s="4">
         <v>0.8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="B13" s="4">
         <v>1.4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="B15" s="4">
-        <v>0.20997644</v>
+        <v>1500</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="3"/>
+        <v>233</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1500</v>
+      </c>
       <c r="C16" s="3" t="s">
-        <v>276</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="B17" s="4">
-        <v>1913</v>
+        <v>60</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>276</v>
+        <v>120</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="B18" s="3">
-        <v>0.6114473499999999</v>
+        <v>14400</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="B19" s="4">
-        <v>1913</v>
+        <v>10</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B20" s="3">
-        <v>8245</v>
+        <v>28800</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>276</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="B21" s="4">
-        <v>0.17857621</v>
+        <v>42</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>113</v>
+        <v>303</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="B22" s="3">
-        <v>8245</v>
+        <v>0.20997644</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>276</v>
+        <v>124</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>299</v>
+        <v>331</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="B24" s="3">
-        <v>0.55</v>
+        <v>1913</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="B25" s="4">
-        <v>0.12</v>
+        <v>0.6114473499999999</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>277</v>
+        <v>124</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="B26" s="3">
-        <v>0.03</v>
+        <v>1913</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="B27" s="4">
-        <v>0</v>
+        <v>8245</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="B28" s="3">
-        <v>6</v>
+        <v>0.17857621</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>278</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="B29" s="4">
-        <v>20</v>
+        <v>8245</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B31" s="4"/>
+        <v>248</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0.55</v>
+      </c>
       <c r="C31" s="4" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="B32" s="3">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="B33" s="4">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="B34" s="3">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="B35" s="4">
-        <v>0.18</v>
+        <v>6</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="B36" s="3">
-        <v>0.14</v>
+        <v>20</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B37" s="4">
-        <v>0.1</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B38" s="3">
-        <v>0.16</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="B39" s="4">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="B40" s="3">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="B41" s="4">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="B42" s="3">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="B43" s="4">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="B44" s="3">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="B45" s="4">
         <v>0.16</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="B46" s="3">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="B47" s="4">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="B48" s="3">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="B49" s="4">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="B50" s="3">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B51" s="4">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="B52" s="3">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="B53" s="4">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="B54" s="3">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="B55" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="B56" s="3">
         <v>0.2</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="B57" s="4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="B58" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="B59" s="4">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="B60" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="B61" s="4">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="B62" s="3">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="B63" s="4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="B64" s="3">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="34" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B65" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B66" s="3">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="34" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="B67" s="4">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="B68" s="3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="34" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="B69" s="4">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="B70" s="3">
         <v>0.1</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="34" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="B71" s="4">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="34" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="B73" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="34" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="34" customHeight="1">
+      <c r="A75" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B75" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="34" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="34" customHeight="1">
+      <c r="A77" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B77" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="34" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="34" customHeight="1">
+      <c r="A79" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B79" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="34" customHeight="1">
+      <c r="A80" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B80" s="3">
         <v>0.7</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>352</v>
+      <c r="C80" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>391</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E73"/>
+  <autoFilter ref="A3:E80"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -4838,7 +5286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -4848,7 +5296,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>420</v>
+        <v>472</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4858,7 +5306,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -4866,259 +5314,314 @@
     </row>
     <row r="4" spans="1:3" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>397</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>398</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>399</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>400</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>401</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>360</v>
+        <v>399</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>402</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>403</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>405</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>407</v>
+        <v>454</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>408</v>
+        <v>455</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>367</v>
+        <v>406</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>387</v>
+        <v>431</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>409</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>410</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>389</v>
+        <v>433</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>411</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>412</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>391</v>
+        <v>435</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>413</v>
+        <v>460</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>372</v>
+        <v>411</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>414</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>373</v>
+        <v>412</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>393</v>
+        <v>437</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>415</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>416</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>417</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>418</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="34" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="34" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="34" customHeight="1">
+      <c r="A29" s="4" t="s">
         <v>419</v>
       </c>
+      <c r="B29" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="34" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="34" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>471</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C26"/>
+  <autoFilter ref="A3:C31"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -5128,7 +5631,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -5137,7 +5640,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -5151,126 +5654,142 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>421</v>
+        <v>473</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>436</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>422</v>
+        <v>474</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>437</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>423</v>
+        <v>475</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>424</v>
+        <v>476</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>439</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>440</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>426</v>
+        <v>478</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>441</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>427</v>
+        <v>479</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>442</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>428</v>
+        <v>480</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>443</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>429</v>
+        <v>481</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>444</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>430</v>
+        <v>482</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>445</v>
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>446</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>432</v>
+        <v>484</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>447</v>
+        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>433</v>
+        <v>485</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>448</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>434</v>
+        <v>486</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>449</v>
+        <v>503</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>450</v>
+        <v>504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="34" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="34" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>506</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B18"/>
+  <autoFilter ref="A3:B20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -5280,7 +5799,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -5289,7 +5808,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>548</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -5303,150 +5822,166 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>452</v>
+        <v>508</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>470</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>453</v>
+        <v>509</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>471</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>454</v>
+        <v>510</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>472</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>455</v>
+        <v>511</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>473</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>456</v>
+        <v>512</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>474</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>475</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>458</v>
+        <v>514</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>476</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>459</v>
+        <v>515</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>477</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>460</v>
+        <v>516</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>478</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>461</v>
+        <v>517</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>479</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>462</v>
+        <v>518</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>480</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>463</v>
+        <v>519</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>481</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>464</v>
+        <v>520</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>482</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>465</v>
+        <v>521</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>483</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>466</v>
+        <v>522</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>484</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>467</v>
+        <v>523</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>485</v>
+        <v>543</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>468</v>
+        <v>524</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>486</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>487</v>
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="34" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="34" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B21"/>
+  <autoFilter ref="A3:B23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -5456,7 +5991,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -5469,7 +6004,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>686</v>
+        <v>749</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5483,42 +6018,42 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>489</v>
+        <v>549</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>491</v>
+        <v>551</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>492</v>
+        <v>552</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>493</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>494</v>
+        <v>554</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>554</v>
+        <v>615</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>624</v>
+        <v>686</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G4" s="3">
         <v>25498039</v>
@@ -5526,22 +6061,22 @@
     </row>
     <row r="5" spans="1:7" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>495</v>
+        <v>555</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>555</v>
+        <v>616</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>625</v>
+        <v>687</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G5" s="4">
         <v>54288508</v>
@@ -5549,22 +6084,22 @@
     </row>
     <row r="6" spans="1:7" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>556</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>556</v>
+        <v>617</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>626</v>
+        <v>688</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G6" s="3">
         <v>43443363</v>
@@ -5572,22 +6107,22 @@
     </row>
     <row r="7" spans="1:7" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>497</v>
+        <v>557</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>557</v>
+        <v>618</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>614</v>
+        <v>676</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>627</v>
+        <v>689</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G7" s="4">
         <v>25498039</v>
@@ -5595,22 +6130,22 @@
     </row>
     <row r="8" spans="1:7" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>498</v>
+        <v>558</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>558</v>
+        <v>619</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>615</v>
+        <v>677</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>628</v>
+        <v>690</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G8" s="3">
         <v>1671168</v>
@@ -5618,22 +6153,22 @@
     </row>
     <row r="9" spans="1:7" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>499</v>
+        <v>559</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>559</v>
+        <v>620</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>615</v>
+        <v>677</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>629</v>
+        <v>691</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G9" s="4">
         <v>1970176</v>
@@ -5641,22 +6176,22 @@
     </row>
     <row r="10" spans="1:7" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>500</v>
+        <v>560</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>560</v>
+        <v>621</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>616</v>
+        <v>678</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>630</v>
+        <v>692</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G10" s="3">
         <v>18419712</v>
@@ -5664,22 +6199,22 @@
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>501</v>
+        <v>561</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>561</v>
+        <v>622</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>616</v>
+        <v>678</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>631</v>
+        <v>693</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G11" s="4">
         <v>26136576</v>
@@ -5687,22 +6222,22 @@
     </row>
     <row r="12" spans="1:7" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>502</v>
+        <v>562</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>562</v>
+        <v>623</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>632</v>
+        <v>694</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G12" s="3">
         <v>7745077</v>
@@ -5710,22 +6245,22 @@
     </row>
     <row r="13" spans="1:7" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>503</v>
+        <v>563</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>563</v>
+        <v>624</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>633</v>
+        <v>695</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G13" s="4">
         <v>503</v>
@@ -5733,22 +6268,22 @@
     </row>
     <row r="14" spans="1:7" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>504</v>
+        <v>564</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>564</v>
+        <v>625</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>634</v>
+        <v>696</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G14" s="3">
         <v>5241</v>
@@ -5756,22 +6291,22 @@
     </row>
     <row r="15" spans="1:7" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>505</v>
+        <v>565</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>565</v>
+        <v>626</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>635</v>
+        <v>697</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G15" s="4">
         <v>16899</v>
@@ -5779,22 +6314,22 @@
     </row>
     <row r="16" spans="1:7" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>506</v>
+        <v>566</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>566</v>
+        <v>627</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>636</v>
+        <v>698</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G16" s="3">
         <v>279475</v>
@@ -5802,22 +6337,22 @@
     </row>
     <row r="17" spans="1:7" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>507</v>
+        <v>567</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>567</v>
+        <v>628</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>637</v>
+        <v>699</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G17" s="4">
         <v>9517009</v>
@@ -5825,22 +6360,22 @@
     </row>
     <row r="18" spans="1:7" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>508</v>
+        <v>568</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>568</v>
+        <v>629</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>638</v>
+        <v>700</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G18" s="3">
         <v>11068</v>
@@ -5848,22 +6383,22 @@
     </row>
     <row r="19" spans="1:7" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>509</v>
+        <v>569</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>569</v>
+        <v>630</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>639</v>
+        <v>701</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G19" s="4">
         <v>14503</v>
@@ -5871,22 +6406,22 @@
     </row>
     <row r="20" spans="1:7" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>570</v>
+        <v>631</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>640</v>
+        <v>702</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G20" s="3">
         <v>11601</v>
@@ -5894,22 +6429,22 @@
     </row>
     <row r="21" spans="1:7" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>511</v>
+        <v>571</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>571</v>
+        <v>632</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>641</v>
+        <v>703</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G21" s="4">
         <v>921600</v>
@@ -5917,22 +6452,22 @@
     </row>
     <row r="22" spans="1:7" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>512</v>
+        <v>572</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>572</v>
+        <v>633</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>642</v>
+        <v>704</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G22" s="3">
         <v>4329472</v>
@@ -5940,64 +6475,64 @@
     </row>
     <row r="23" spans="1:7" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>513</v>
+        <v>573</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>573</v>
+        <v>634</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>514</v>
+        <v>574</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>574</v>
+        <v>635</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>644</v>
+        <v>706</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>515</v>
+        <v>575</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>575</v>
+        <v>636</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>645</v>
+        <v>707</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G25" s="4">
         <v>5040</v>
@@ -6005,22 +6540,22 @@
     </row>
     <row r="26" spans="1:7" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>516</v>
+        <v>576</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>576</v>
+        <v>637</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>646</v>
+        <v>708</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G26" s="3">
         <v>1136</v>
@@ -6028,22 +6563,22 @@
     </row>
     <row r="27" spans="1:7" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>517</v>
+        <v>577</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>577</v>
+        <v>638</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>617</v>
+        <v>679</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>647</v>
+        <v>709</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G27" s="4">
         <v>765</v>
@@ -6051,22 +6586,22 @@
     </row>
     <row r="28" spans="1:7" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>518</v>
+        <v>578</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>578</v>
+        <v>639</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>618</v>
+        <v>680</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>648</v>
+        <v>710</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G28" s="3">
         <v>1069056</v>
@@ -6074,22 +6609,22 @@
     </row>
     <row r="29" spans="1:7" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>579</v>
+        <v>640</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>618</v>
+        <v>680</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>649</v>
+        <v>711</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G29" s="4">
         <v>187087</v>
@@ -6097,22 +6632,22 @@
     </row>
     <row r="30" spans="1:7" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>520</v>
+        <v>580</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>580</v>
+        <v>641</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>618</v>
+        <v>680</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>650</v>
+        <v>712</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G30" s="3">
         <v>50224012</v>
@@ -6120,22 +6655,22 @@
     </row>
     <row r="31" spans="1:7" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>521</v>
+        <v>581</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>581</v>
+        <v>642</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>618</v>
+        <v>680</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>651</v>
+        <v>713</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G31" s="4">
         <v>228006</v>
@@ -6143,22 +6678,22 @@
     </row>
     <row r="32" spans="1:7" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>522</v>
+        <v>582</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>582</v>
+        <v>643</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>618</v>
+        <v>680</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>652</v>
+        <v>714</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G32" s="3">
         <v>3123</v>
@@ -6166,45 +6701,45 @@
     </row>
     <row r="33" spans="1:7" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>523</v>
+        <v>583</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>583</v>
+        <v>644</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>618</v>
+        <v>680</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>653</v>
+        <v>715</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G33" s="4">
-        <v>683</v>
+        <v>840</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>524</v>
+        <v>584</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>584</v>
+        <v>645</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>619</v>
+        <v>681</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>654</v>
+        <v>716</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G34" s="3">
         <v>227102</v>
@@ -6212,22 +6747,22 @@
     </row>
     <row r="35" spans="1:7" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>525</v>
+        <v>585</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>585</v>
+        <v>646</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>619</v>
+        <v>681</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>655</v>
+        <v>717</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G35" s="4">
         <v>224907</v>
@@ -6235,22 +6770,22 @@
     </row>
     <row r="36" spans="1:7" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>526</v>
+        <v>586</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>586</v>
+        <v>647</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>619</v>
+        <v>681</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>656</v>
+        <v>718</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G36" s="3">
         <v>451839</v>
@@ -6258,22 +6793,22 @@
     </row>
     <row r="37" spans="1:7" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>587</v>
+        <v>648</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>620</v>
+        <v>682</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>657</v>
+        <v>719</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G37" s="4">
         <v>1288420</v>
@@ -6281,22 +6816,22 @@
     </row>
     <row r="38" spans="1:7" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>528</v>
+        <v>588</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>588</v>
+        <v>649</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>620</v>
+        <v>682</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G38" s="3">
         <v>1314652</v>
@@ -6304,22 +6839,22 @@
     </row>
     <row r="39" spans="1:7" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>529</v>
+        <v>589</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>589</v>
+        <v>650</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>620</v>
+        <v>682</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>659</v>
+        <v>721</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G39" s="4">
         <v>2602915</v>
@@ -6327,22 +6862,22 @@
     </row>
     <row r="40" spans="1:7" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>530</v>
+        <v>590</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>590</v>
+        <v>651</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>660</v>
+        <v>722</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G40" s="3">
         <v>2109747</v>
@@ -6350,22 +6885,22 @@
     </row>
     <row r="41" spans="1:7" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>531</v>
+        <v>591</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>591</v>
+        <v>652</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>661</v>
+        <v>723</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G41" s="4">
         <v>2106524</v>
@@ -6373,22 +6908,22 @@
     </row>
     <row r="42" spans="1:7" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>532</v>
+        <v>592</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>592</v>
+        <v>653</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>662</v>
+        <v>724</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G42" s="3">
         <v>4216067</v>
@@ -6396,22 +6931,22 @@
     </row>
     <row r="43" spans="1:7" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>533</v>
+        <v>593</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>593</v>
+        <v>654</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>663</v>
+        <v>725</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G43" s="4">
         <v>15617568</v>
@@ -6419,22 +6954,22 @@
     </row>
     <row r="44" spans="1:7" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>534</v>
+        <v>594</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>594</v>
+        <v>655</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>664</v>
+        <v>726</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G44" s="3">
         <v>556</v>
@@ -6442,22 +6977,22 @@
     </row>
     <row r="45" spans="1:7" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>535</v>
+        <v>595</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>595</v>
+        <v>656</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>665</v>
+        <v>727</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G45" s="4">
         <v>525</v>
@@ -6465,22 +7000,22 @@
     </row>
     <row r="46" spans="1:7" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>536</v>
+        <v>596</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>596</v>
+        <v>657</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>666</v>
+        <v>728</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G46" s="3">
         <v>17707008</v>
@@ -6488,22 +7023,22 @@
     </row>
     <row r="47" spans="1:7" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>597</v>
+        <v>658</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>667</v>
+        <v>729</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G47" s="4">
         <v>714918</v>
@@ -6511,22 +7046,22 @@
     </row>
     <row r="48" spans="1:7" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>538</v>
+        <v>598</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>598</v>
+        <v>659</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>668</v>
+        <v>730</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G48" s="3">
         <v>745255</v>
@@ -6534,22 +7069,22 @@
     </row>
     <row r="49" spans="1:7" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>599</v>
+        <v>660</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>669</v>
+        <v>731</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G49" s="4">
         <v>1459825</v>
@@ -6557,22 +7092,22 @@
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>600</v>
+        <v>661</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>670</v>
+        <v>732</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G50" s="3">
         <v>20062208</v>
@@ -6580,22 +7115,22 @@
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>541</v>
+        <v>601</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>601</v>
+        <v>662</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>671</v>
+        <v>733</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G51" s="4">
         <v>20447232</v>
@@ -6603,22 +7138,22 @@
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>602</v>
+        <v>663</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>621</v>
+        <v>683</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>672</v>
+        <v>734</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G52" s="3">
         <v>2492663</v>
@@ -6626,22 +7161,22 @@
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>543</v>
+        <v>603</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>603</v>
+        <v>664</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>621</v>
+        <v>683</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>673</v>
+        <v>735</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G53" s="4">
         <v>704</v>
@@ -6649,22 +7184,22 @@
     </row>
     <row r="54" spans="1:7" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>544</v>
+        <v>604</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>604</v>
+        <v>665</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>621</v>
+        <v>683</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>674</v>
+        <v>736</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G54" s="3">
         <v>23400448</v>
@@ -6672,22 +7207,22 @@
     </row>
     <row r="55" spans="1:7" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>545</v>
+        <v>605</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>605</v>
+        <v>666</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>675</v>
+        <v>737</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G55" s="4">
         <v>1094788</v>
@@ -6695,22 +7230,22 @@
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>546</v>
+        <v>606</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>606</v>
+        <v>667</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>676</v>
+        <v>738</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G56" s="3">
         <v>870164</v>
@@ -6718,22 +7253,22 @@
     </row>
     <row r="57" spans="1:7" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>547</v>
+        <v>607</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>607</v>
+        <v>668</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>677</v>
+        <v>739</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G57" s="4">
         <v>1095579</v>
@@ -6741,22 +7276,22 @@
     </row>
     <row r="58" spans="1:7" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>548</v>
+        <v>608</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>608</v>
+        <v>669</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>678</v>
+        <v>740</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G58" s="3">
         <v>877549</v>
@@ -6764,22 +7299,22 @@
     </row>
     <row r="59" spans="1:7" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>549</v>
+        <v>609</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>609</v>
+        <v>670</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>679</v>
+        <v>741</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G59" s="4">
         <v>940952</v>
@@ -6787,22 +7322,22 @@
     </row>
     <row r="60" spans="1:7" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>610</v>
+        <v>671</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>680</v>
+        <v>742</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G60" s="3">
         <v>854357</v>
@@ -6810,22 +7345,22 @@
     </row>
     <row r="61" spans="1:7" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>611</v>
+        <v>672</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>622</v>
+        <v>684</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>681</v>
+        <v>743</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>685</v>
+        <v>748</v>
       </c>
       <c r="G61" s="4">
         <v>542</v>
@@ -6833,48 +7368,75 @@
     </row>
     <row r="62" spans="1:7" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>552</v>
+        <v>612</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>612</v>
+        <v>673</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>623</v>
+        <v>110</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>682</v>
+        <v>744</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="G62" s="3"/>
+        <v>748</v>
+      </c>
+      <c r="G62" s="3">
+        <v>28018</v>
+      </c>
     </row>
     <row r="63" spans="1:7" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>553</v>
+        <v>613</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>613</v>
+        <v>674</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>623</v>
+        <v>685</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>683</v>
+        <v>745</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>684</v>
+        <v>747</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="G63" s="4">
+        <v>27141</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="34" customHeight="1">
+      <c r="A64" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="G63" s="4"/>
+      <c r="D64" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="G64" s="3">
+        <v>74339</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G63"/>
+  <autoFilter ref="A3:G64"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/outputs/metadados_piloto.xlsx
+++ b/outputs/metadados_piloto.xlsx
@@ -16,20 +16,20 @@
     <sheet name="Arquivos gerados" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resumo!$A$3:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="767">
   <si>
     <t>campo</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Piloto computacional de mobilidade urbana, diferenciação socioespacial e entropia socioeconômica de trajetórias</t>
   </si>
   <si>
-    <t>2026-09-28T07:41:40.727776+00:00</t>
+    <t>2026-09-28T07:52:52.803295+00:00</t>
   </si>
   <si>
     <t>português</t>
@@ -319,6 +319,12 @@
     <t>mean_in_vehicle_time_per_connection_s</t>
   </si>
   <si>
+    <t>missing_stop_time_summary</t>
+  </si>
+  <si>
+    <t>missing_connection_summary</t>
+  </si>
+  <si>
     <t>egress_walk_distance_m</t>
   </si>
   <si>
@@ -367,6 +373,9 @@
     <t>diagnóstico de transporte coletivo</t>
   </si>
   <si>
+    <t>qualidade temporal do GTFS</t>
+  </si>
+  <si>
     <t>identificador</t>
   </si>
   <si>
@@ -682,6 +691,12 @@
     <t>Tempo médio dentro do veículo por conexão GTFS usada na rota, empregado como diagnóstico de qualidade temporal</t>
   </si>
   <si>
+    <t>Indica viagem sem resumo temporal derivado de stop_times após a associação por trip_id</t>
+  </si>
+  <si>
+    <t>Indica viagem sem conexões temporais processadas após a associação por trip_id</t>
+  </si>
+  <si>
     <t>Distância total percorrida a pé entre a parada de desembarque e o destino</t>
   </si>
   <si>
@@ -1297,6 +1312,9 @@
     <t>Validação de continuidade do itinerário de transporte coletivo</t>
   </si>
   <si>
+    <t>Diagnóstico temporal por viagem GTFS</t>
+  </si>
+  <si>
     <t>generate_population</t>
   </si>
   <si>
@@ -1363,6 +1381,9 @@
     <t>run_diagnostics</t>
   </si>
   <si>
+    <t>build_trip_temporal_quality</t>
+  </si>
+  <si>
     <t>Gera agentes sintéticos preservando as participações configuradas para os grupos de renda</t>
   </si>
   <si>
@@ -1447,6 +1468,9 @@
     <t>Exige continuidade entre a parada de destino de uma conexão e a parada de origem da conexão seguinte e preserva a ordem numérica de stop_sequence em empates temporais</t>
   </si>
   <si>
+    <t>Resume por trip_id a quantidade de pontos temporais originais, a duração programada, a incidência de conexões de duração zero e a velocidade implícita pelo comprimento do shape</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Métodos de análise</t>
   </si>
   <si>
@@ -1501,6 +1525,12 @@
     <t>Tempo médio por conexão veicular</t>
   </si>
   <si>
+    <t>Velocidade implícita pelo shape</t>
+  </si>
+  <si>
+    <t>Participação de conexões de duração zero por viagem</t>
+  </si>
+  <si>
     <t>Quantifica agentes, viagens, arestas, segmentos, paradas, rotas, shapes e demais unidades discretas</t>
   </si>
   <si>
@@ -1552,6 +1582,12 @@
     <t>Divide o tempo dentro do veículo pelo número de conexões GTFS usadas na rota para identificar itinerários temporalmente suspeitos</t>
   </si>
   <si>
+    <t>Relaciona o comprimento geométrico do shape à duração programada da viagem para diagnosticar a coerência temporal do GTFS processado</t>
+  </si>
+  <si>
+    <t>Mede a proporção de conexões consecutivas com tempo veicular igual a zero dentro de cada trip_id</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Estatísticas</t>
   </si>
   <si>
@@ -1615,6 +1651,9 @@
     <t>Validação de continuidade entre conexões GTFS</t>
   </si>
   <si>
+    <t>Preservação explícita de valores ausentes em diagnósticos temporais</t>
+  </si>
+  <si>
     <t>Remove espaços excedentes e normaliza campos textuais usados como identificadores e categorias</t>
   </si>
   <si>
@@ -1675,6 +1714,9 @@
     <t>Confere se cada conexão do itinerário começa na parada onde a conexão anterior terminou antes de aceitar o resultado do roteamento</t>
   </si>
   <si>
+    <t>Mantém viagens sem duração ou sem conexões como valores ausentes e evita classificá-las como duração não positiva ou como baixa quantidade de pontos temporais</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Métodos de limpeza</t>
   </si>
   <si>
@@ -1870,6 +1912,9 @@
     <t>transit_routing_diagnostics.csv</t>
   </si>
   <si>
+    <t>gtfs_trip_temporal_quality.csv</t>
+  </si>
+  <si>
     <t>metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -2053,6 +2098,9 @@
     <t>outputs/pilot/transit_routing_diagnostics.csv</t>
   </si>
   <si>
+    <t>outputs/pilot/gtfs_trip_temporal_quality.csv</t>
+  </si>
+  <si>
     <t>outputs/metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -2264,6 +2312,9 @@
   </si>
   <si>
     <t>Amostra de consultas origem-destino usada para validar cobertura, tempos, acesso, egresso e transferências do roteador temporal de ônibus</t>
+  </si>
+  <si>
+    <t>Diagnóstico por trip_id com duração programada, pontos temporais originais, conexões de duração zero e velocidade implícita pelo shape</t>
   </si>
   <si>
     <t>Planilha consolidada com variáveis, parâmetros, métodos, estatísticas, limpeza e arquivos do piloto</t>
@@ -2744,7 +2795,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
@@ -2752,7 +2803,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
@@ -2760,7 +2811,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
@@ -2768,7 +2819,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
@@ -2776,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2790,7 +2841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2801,7 +2852,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2826,13 +2877,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
@@ -2840,13 +2891,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
@@ -2854,13 +2905,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
@@ -2868,13 +2919,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
@@ -2882,13 +2933,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
@@ -2896,13 +2947,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="34" customHeight="1">
@@ -2910,13 +2961,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34" customHeight="1">
@@ -2924,13 +2975,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1">
@@ -2938,13 +2989,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34" customHeight="1">
@@ -2952,13 +3003,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34" customHeight="1">
@@ -2966,13 +3017,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="34" customHeight="1">
@@ -2980,13 +3031,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34" customHeight="1">
@@ -2994,13 +3045,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="34" customHeight="1">
@@ -3008,13 +3059,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34" customHeight="1">
@@ -3022,13 +3073,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="34" customHeight="1">
@@ -3036,13 +3087,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="34" customHeight="1">
@@ -3050,13 +3101,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" customHeight="1">
@@ -3064,13 +3115,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" customHeight="1">
@@ -3078,13 +3129,13 @@
         <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" customHeight="1">
@@ -3092,13 +3143,13 @@
         <v>39</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" customHeight="1">
@@ -3106,13 +3157,13 @@
         <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="34" customHeight="1">
@@ -3120,13 +3171,13 @@
         <v>41</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="34" customHeight="1">
@@ -3134,13 +3185,13 @@
         <v>42</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="34" customHeight="1">
@@ -3148,13 +3199,13 @@
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="34" customHeight="1">
@@ -3162,13 +3213,13 @@
         <v>44</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="34" customHeight="1">
@@ -3176,13 +3227,13 @@
         <v>45</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="34" customHeight="1">
@@ -3190,13 +3241,13 @@
         <v>46</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="34" customHeight="1">
@@ -3204,13 +3255,13 @@
         <v>47</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="34" customHeight="1">
@@ -3218,13 +3269,13 @@
         <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="34" customHeight="1">
@@ -3232,13 +3283,13 @@
         <v>49</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="34" customHeight="1">
@@ -3246,13 +3297,13 @@
         <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="34" customHeight="1">
@@ -3260,13 +3311,13 @@
         <v>51</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="34" customHeight="1">
@@ -3274,13 +3325,13 @@
         <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="34" customHeight="1">
@@ -3288,13 +3339,13 @@
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" customHeight="1">
@@ -3302,13 +3353,13 @@
         <v>54</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="34" customHeight="1">
@@ -3316,13 +3367,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="34" customHeight="1">
@@ -3330,13 +3381,13 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="34" customHeight="1">
@@ -3344,13 +3395,13 @@
         <v>57</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="34" customHeight="1">
@@ -3358,13 +3409,13 @@
         <v>58</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" customHeight="1">
@@ -3372,13 +3423,13 @@
         <v>59</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="34" customHeight="1">
@@ -3386,13 +3437,13 @@
         <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="34" customHeight="1">
@@ -3400,13 +3451,13 @@
         <v>61</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="34" customHeight="1">
@@ -3414,13 +3465,13 @@
         <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="34" customHeight="1">
@@ -3428,13 +3479,13 @@
         <v>63</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="34" customHeight="1">
@@ -3442,13 +3493,13 @@
         <v>64</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="34" customHeight="1">
@@ -3456,13 +3507,13 @@
         <v>65</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="34" customHeight="1">
@@ -3470,13 +3521,13 @@
         <v>66</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="34" customHeight="1">
@@ -3484,13 +3535,13 @@
         <v>67</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="34" customHeight="1">
@@ -3498,13 +3549,13 @@
         <v>68</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="34" customHeight="1">
@@ -3512,13 +3563,13 @@
         <v>69</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="34" customHeight="1">
@@ -3526,13 +3577,13 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="34" customHeight="1">
@@ -3540,13 +3591,13 @@
         <v>71</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="34" customHeight="1">
@@ -3554,13 +3605,13 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="34" customHeight="1">
@@ -3568,13 +3619,13 @@
         <v>73</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="34" customHeight="1">
@@ -3582,13 +3633,13 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="34" customHeight="1">
@@ -3596,13 +3647,13 @@
         <v>75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="34" customHeight="1">
@@ -3610,13 +3661,13 @@
         <v>76</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="34" customHeight="1">
@@ -3624,13 +3675,13 @@
         <v>77</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="34" customHeight="1">
@@ -3638,13 +3689,13 @@
         <v>78</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="34" customHeight="1">
@@ -3652,13 +3703,13 @@
         <v>79</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="34" customHeight="1">
@@ -3666,13 +3717,13 @@
         <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="34" customHeight="1">
@@ -3680,13 +3731,13 @@
         <v>81</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="34" customHeight="1">
@@ -3694,13 +3745,13 @@
         <v>82</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="34" customHeight="1">
@@ -3708,13 +3759,13 @@
         <v>83</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="34" customHeight="1">
@@ -3722,13 +3773,13 @@
         <v>84</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="34" customHeight="1">
@@ -3736,13 +3787,13 @@
         <v>85</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="34" customHeight="1">
@@ -3750,13 +3801,13 @@
         <v>86</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="34" customHeight="1">
@@ -3764,13 +3815,13 @@
         <v>87</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="34" customHeight="1">
@@ -3778,13 +3829,13 @@
         <v>88</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="34" customHeight="1">
@@ -3792,13 +3843,13 @@
         <v>89</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="34" customHeight="1">
@@ -3806,13 +3857,13 @@
         <v>90</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="34" customHeight="1">
@@ -3820,13 +3871,13 @@
         <v>91</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="34" customHeight="1">
@@ -3834,13 +3885,13 @@
         <v>87</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="34" customHeight="1">
@@ -3848,13 +3899,13 @@
         <v>92</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="34" customHeight="1">
@@ -3862,13 +3913,13 @@
         <v>93</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="34" customHeight="1">
@@ -3876,13 +3927,13 @@
         <v>94</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="34" customHeight="1">
@@ -3890,13 +3941,13 @@
         <v>95</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="34" customHeight="1">
@@ -3904,13 +3955,13 @@
         <v>96</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="34" customHeight="1">
@@ -3918,17 +3969,45 @@
         <v>97</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="34" customHeight="1">
+      <c r="A83" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="34" customHeight="1">
+      <c r="A84" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D82"/>
+  <autoFilter ref="A3:D84"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -3950,7 +4029,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3971,1308 +4050,1308 @@
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B4" s="3">
         <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B5" s="4">
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B7" s="4">
         <v>30000</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B9" s="4">
         <v>0.8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B13" s="4">
         <v>1.4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B15" s="4">
         <v>1500</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B16" s="3">
         <v>1500</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B17" s="4">
         <v>60</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B18" s="3">
         <v>14400</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B19" s="4">
         <v>10</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B20" s="3">
         <v>28800</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B21" s="4">
         <v>42</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B22" s="3">
         <v>0.20997644</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B24" s="3">
         <v>1913</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B25" s="4">
         <v>0.6114473499999999</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B26" s="3">
         <v>1913</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B27" s="4">
         <v>8245</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B28" s="3">
         <v>0.17857621</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B29" s="4">
         <v>8245</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B31" s="4">
         <v>0.55</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B32" s="3">
         <v>0.12</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B33" s="4">
         <v>0.03</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B35" s="4">
         <v>6</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B36" s="3">
         <v>20</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B39" s="4">
         <v>0.1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B40" s="3">
         <v>0.09</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B41" s="4">
         <v>0.08</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B42" s="3">
         <v>0.18</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B43" s="4">
         <v>0.14</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B44" s="3">
         <v>0.1</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B45" s="4">
         <v>0.16</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B46" s="3">
         <v>0.13</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B47" s="4">
         <v>0.1</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B48" s="3">
         <v>0.25</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B49" s="4">
         <v>0.15</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B50" s="3">
         <v>0.08</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B51" s="4">
         <v>0.28</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B52" s="3">
         <v>0.16</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B53" s="4">
         <v>0.08</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B54" s="3">
         <v>0.45</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B55" s="4">
         <v>0.15</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B56" s="3">
         <v>0.2</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B57" s="4">
         <v>0.1</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B59" s="4">
         <v>0.35</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B61" s="4">
         <v>0.2</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B62" s="3">
         <v>0.1</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B63" s="4">
         <v>0.2</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B64" s="3">
         <v>0.3</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="34" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B65" s="4">
         <v>0.15</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B66" s="3">
         <v>0.2</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="34" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B67" s="4">
         <v>0.1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B68" s="3">
         <v>0.25</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="34" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B69" s="4">
         <v>0.25</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B70" s="3">
         <v>0.1</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="34" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B71" s="4">
         <v>0.55</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="34" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B73" s="4">
         <v>0.15</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="34" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="34" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B75" s="4">
         <v>0.3</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="34" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B76" s="3">
         <v>0.4</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="34" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B77" s="4">
         <v>0.1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="34" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B78" s="3">
         <v>0.1</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="34" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B79" s="4">
         <v>0.1</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="34" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B80" s="3">
         <v>0.7</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -5286,7 +5365,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -5296,7 +5375,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5306,7 +5385,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -5314,314 +5393,325 @@
     </row>
     <row r="4" spans="1:3" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>471</v>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="34" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C31"/>
+  <autoFilter ref="A3:C32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -5631,7 +5721,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -5640,7 +5730,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -5654,142 +5744,158 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>506</v>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="34" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="34" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B20"/>
+  <autoFilter ref="A3:B22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -5799,7 +5905,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -5808,7 +5914,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -5822,166 +5928,174 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>547</v>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="34" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B23"/>
+  <autoFilter ref="A3:B24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -5991,7 +6105,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -6004,7 +6118,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>749</v>
+        <v>766</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6018,42 +6132,42 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G4" s="3">
         <v>25498039</v>
@@ -6061,22 +6175,22 @@
     </row>
     <row r="5" spans="1:7" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G5" s="4">
         <v>54288508</v>
@@ -6084,22 +6198,22 @@
     </row>
     <row r="6" spans="1:7" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G6" s="3">
         <v>43443363</v>
@@ -6107,22 +6221,22 @@
     </row>
     <row r="7" spans="1:7" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G7" s="4">
         <v>25498039</v>
@@ -6130,22 +6244,22 @@
     </row>
     <row r="8" spans="1:7" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G8" s="3">
         <v>1671168</v>
@@ -6153,22 +6267,22 @@
     </row>
     <row r="9" spans="1:7" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G9" s="4">
         <v>1970176</v>
@@ -6176,22 +6290,22 @@
     </row>
     <row r="10" spans="1:7" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G10" s="3">
         <v>18419712</v>
@@ -6199,22 +6313,22 @@
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G11" s="4">
         <v>26136576</v>
@@ -6222,22 +6336,22 @@
     </row>
     <row r="12" spans="1:7" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G12" s="3">
         <v>7745077</v>
@@ -6245,22 +6359,22 @@
     </row>
     <row r="13" spans="1:7" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G13" s="4">
         <v>503</v>
@@ -6268,22 +6382,22 @@
     </row>
     <row r="14" spans="1:7" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G14" s="3">
         <v>5241</v>
@@ -6291,22 +6405,22 @@
     </row>
     <row r="15" spans="1:7" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G15" s="4">
         <v>16899</v>
@@ -6314,22 +6428,22 @@
     </row>
     <row r="16" spans="1:7" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>627</v>
+        <v>642</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G16" s="3">
         <v>279475</v>
@@ -6337,22 +6451,22 @@
     </row>
     <row r="17" spans="1:7" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>628</v>
+        <v>643</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G17" s="4">
         <v>9517009</v>
@@ -6360,22 +6474,22 @@
     </row>
     <row r="18" spans="1:7" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G18" s="3">
         <v>11068</v>
@@ -6383,22 +6497,22 @@
     </row>
     <row r="19" spans="1:7" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>630</v>
+        <v>645</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G19" s="4">
         <v>14503</v>
@@ -6406,22 +6520,22 @@
     </row>
     <row r="20" spans="1:7" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>631</v>
+        <v>646</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G20" s="3">
         <v>11601</v>
@@ -6429,22 +6543,22 @@
     </row>
     <row r="21" spans="1:7" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G21" s="4">
         <v>921600</v>
@@ -6452,22 +6566,22 @@
     </row>
     <row r="22" spans="1:7" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>633</v>
+        <v>648</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G22" s="3">
         <v>4329472</v>
@@ -6475,64 +6589,64 @@
     </row>
     <row r="23" spans="1:7" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>634</v>
+        <v>649</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>635</v>
+        <v>650</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>636</v>
+        <v>651</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G25" s="4">
         <v>5040</v>
@@ -6540,22 +6654,22 @@
     </row>
     <row r="26" spans="1:7" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>708</v>
+        <v>724</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G26" s="3">
         <v>1136</v>
@@ -6563,22 +6677,22 @@
     </row>
     <row r="27" spans="1:7" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G27" s="4">
         <v>765</v>
@@ -6586,22 +6700,22 @@
     </row>
     <row r="28" spans="1:7" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G28" s="3">
         <v>1069056</v>
@@ -6609,22 +6723,22 @@
     </row>
     <row r="29" spans="1:7" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G29" s="4">
         <v>187087</v>
@@ -6632,22 +6746,22 @@
     </row>
     <row r="30" spans="1:7" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G30" s="3">
         <v>50224012</v>
@@ -6655,22 +6769,22 @@
     </row>
     <row r="31" spans="1:7" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G31" s="4">
         <v>228006</v>
@@ -6678,22 +6792,22 @@
     </row>
     <row r="32" spans="1:7" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G32" s="3">
         <v>3123</v>
@@ -6701,22 +6815,22 @@
     </row>
     <row r="33" spans="1:7" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G33" s="4">
         <v>840</v>
@@ -6724,22 +6838,22 @@
     </row>
     <row r="34" spans="1:7" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G34" s="3">
         <v>227102</v>
@@ -6747,22 +6861,22 @@
     </row>
     <row r="35" spans="1:7" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>646</v>
+        <v>661</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>717</v>
+        <v>733</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G35" s="4">
         <v>224907</v>
@@ -6770,22 +6884,22 @@
     </row>
     <row r="36" spans="1:7" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>647</v>
+        <v>662</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>718</v>
+        <v>734</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G36" s="3">
         <v>451839</v>
@@ -6793,22 +6907,22 @@
     </row>
     <row r="37" spans="1:7" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>648</v>
+        <v>663</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>719</v>
+        <v>735</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G37" s="4">
         <v>1288420</v>
@@ -6816,22 +6930,22 @@
     </row>
     <row r="38" spans="1:7" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>649</v>
+        <v>664</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>720</v>
+        <v>736</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G38" s="3">
         <v>1314652</v>
@@ -6839,22 +6953,22 @@
     </row>
     <row r="39" spans="1:7" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G39" s="4">
         <v>2602915</v>
@@ -6862,22 +6976,22 @@
     </row>
     <row r="40" spans="1:7" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G40" s="3">
         <v>2109747</v>
@@ -6885,22 +6999,22 @@
     </row>
     <row r="41" spans="1:7" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G41" s="4">
         <v>2106524</v>
@@ -6908,22 +7022,22 @@
     </row>
     <row r="42" spans="1:7" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>653</v>
+        <v>668</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>724</v>
+        <v>740</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G42" s="3">
         <v>4216067</v>
@@ -6931,22 +7045,22 @@
     </row>
     <row r="43" spans="1:7" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>725</v>
+        <v>741</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G43" s="4">
         <v>15617568</v>
@@ -6954,22 +7068,22 @@
     </row>
     <row r="44" spans="1:7" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>726</v>
+        <v>742</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G44" s="3">
         <v>556</v>
@@ -6977,22 +7091,22 @@
     </row>
     <row r="45" spans="1:7" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>727</v>
+        <v>743</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G45" s="4">
         <v>525</v>
@@ -7000,22 +7114,22 @@
     </row>
     <row r="46" spans="1:7" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>728</v>
+        <v>744</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G46" s="3">
         <v>17707008</v>
@@ -7023,22 +7137,22 @@
     </row>
     <row r="47" spans="1:7" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>729</v>
+        <v>745</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G47" s="4">
         <v>714918</v>
@@ -7046,22 +7160,22 @@
     </row>
     <row r="48" spans="1:7" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G48" s="3">
         <v>745255</v>
@@ -7069,22 +7183,22 @@
     </row>
     <row r="49" spans="1:7" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>731</v>
+        <v>747</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G49" s="4">
         <v>1459825</v>
@@ -7092,22 +7206,22 @@
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>661</v>
+        <v>676</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>732</v>
+        <v>748</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G50" s="3">
         <v>20062208</v>
@@ -7115,22 +7229,22 @@
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>733</v>
+        <v>749</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G51" s="4">
         <v>20447232</v>
@@ -7138,22 +7252,22 @@
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>734</v>
+        <v>750</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G52" s="3">
         <v>2492663</v>
@@ -7161,22 +7275,22 @@
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>735</v>
+        <v>751</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G53" s="4">
         <v>704</v>
@@ -7184,22 +7298,22 @@
     </row>
     <row r="54" spans="1:7" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G54" s="3">
         <v>23400448</v>
@@ -7207,22 +7321,22 @@
     </row>
     <row r="55" spans="1:7" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>737</v>
+        <v>753</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G55" s="4">
         <v>1094788</v>
@@ -7230,22 +7344,22 @@
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>738</v>
+        <v>754</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G56" s="3">
         <v>870164</v>
@@ -7253,22 +7367,22 @@
     </row>
     <row r="57" spans="1:7" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>668</v>
+        <v>683</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>739</v>
+        <v>755</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G57" s="4">
         <v>1095579</v>
@@ -7276,22 +7390,22 @@
     </row>
     <row r="58" spans="1:7" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>669</v>
+        <v>684</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>740</v>
+        <v>756</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G58" s="3">
         <v>877549</v>
@@ -7299,22 +7413,22 @@
     </row>
     <row r="59" spans="1:7" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>741</v>
+        <v>757</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G59" s="4">
         <v>940952</v>
@@ -7322,22 +7436,22 @@
     </row>
     <row r="60" spans="1:7" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>671</v>
+        <v>686</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G60" s="3">
         <v>854357</v>
@@ -7345,22 +7459,22 @@
     </row>
     <row r="61" spans="1:7" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>672</v>
+        <v>687</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G61" s="4">
         <v>542</v>
@@ -7368,22 +7482,22 @@
     </row>
     <row r="62" spans="1:7" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>744</v>
+        <v>760</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G62" s="3">
         <v>28018</v>
@@ -7391,52 +7505,75 @@
     </row>
     <row r="63" spans="1:7" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>685</v>
+        <v>114</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G63" s="4">
-        <v>27141</v>
+        <v>5915237</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="G64" s="3">
+        <v>27138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="34" customHeight="1">
+      <c r="A65" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="G65" s="4">
         <v>74339</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G64"/>
+  <autoFilter ref="A3:G65"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/outputs/metadados_piloto.xlsx
+++ b/outputs/metadados_piloto.xlsx
@@ -16,20 +16,20 @@
     <sheet name="Arquivos gerados" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resumo!$A$3:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="798">
   <si>
     <t>campo</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Piloto computacional de mobilidade urbana, diferenciação socioespacial e entropia socioeconômica de trajetórias</t>
   </si>
   <si>
-    <t>2026-09-28T07:52:52.803295+00:00</t>
+    <t>2026-09-28T08:30:55.189767+00:00</t>
   </si>
   <si>
     <t>português</t>
@@ -271,6 +271,21 @@
     <t>time_interpolation_method</t>
   </si>
   <si>
+    <t>time_regularized</t>
+  </si>
+  <si>
+    <t>time_regularization_method</t>
+  </si>
+  <si>
+    <t>temporal_regularization_feasible</t>
+  </si>
+  <si>
+    <t>routable_for_transit</t>
+  </si>
+  <si>
+    <t>routing_quality_status</t>
+  </si>
+  <si>
     <t>shape_position_m</t>
   </si>
   <si>
@@ -364,6 +379,9 @@
     <t>GTFS</t>
   </si>
   <si>
+    <t>qualidade temporal do GTFS</t>
+  </si>
+  <si>
     <t>transporte coletivo</t>
   </si>
   <si>
@@ -373,9 +391,6 @@
     <t>diagnóstico de transporte coletivo</t>
   </si>
   <si>
-    <t>qualidade temporal do GTFS</t>
-  </si>
-  <si>
     <t>identificador</t>
   </si>
   <si>
@@ -640,6 +655,21 @@
     <t>Método usado para estimar o horário entre shape_dist_traveled, geometria do shape ou stop_sequence</t>
   </si>
   <si>
+    <t>Indica que um horário intermediário foi reconstruído para preservar intervalos positivos entre paradas consecutivas</t>
+  </si>
+  <si>
+    <t>Registra se a reconstrução temporal positiva usa distância pela geometria do shape ou distribuição por stop_sequence</t>
+  </si>
+  <si>
+    <t>Indica se os horários-âncora permitem distribuir pelo menos o intervalo mínimo configurado entre todas as paradas consecutivas</t>
+  </si>
+  <si>
+    <t>Indica se a viagem atende aos critérios técnicos atuais para integrar a tabela usada pelo roteador de transporte coletivo</t>
+  </si>
+  <si>
+    <t>Resume os motivos técnicos pelos quais uma viagem é mantida ou retirada da tabela de conexões usada no roteamento</t>
+  </si>
+  <si>
     <t>Posição projetada da parada ao longo da geometria do shape</t>
   </si>
   <si>
@@ -742,6 +772,12 @@
     <t>transit.network.service_date_strategy</t>
   </si>
   <si>
+    <t>transit.gtfs.temporal_reconstruction.minimum_interval_s</t>
+  </si>
+  <si>
+    <t>transit.routing.quality_filter.max_implied_shape_speed_kmh</t>
+  </si>
+  <si>
     <t>transit.routing.max_access_walk_m</t>
   </si>
   <si>
@@ -967,6 +1003,9 @@
     <t>m/s</t>
   </si>
   <si>
+    <t>km/h</t>
+  </si>
+  <si>
     <t>viagens OD</t>
   </si>
   <si>
@@ -1015,6 +1054,12 @@
     <t>Regra usada para selecionar uma data de serviço representativa do feed</t>
   </si>
   <si>
+    <t>Intervalo temporal mínimo técnico distribuído entre paradas consecutivas durante a reconstrução de horários intermediários</t>
+  </si>
+  <si>
+    <t>Limite técnico provisório usado para impedir que viagens com velocidade média implícita extrema entrem no roteador</t>
+  </si>
+  <si>
     <t>Distância máxima de caminhada entre a origem e uma parada candidata de embarque</t>
   </si>
   <si>
@@ -1288,6 +1333,12 @@
     <t>Interpolação temporal GTFS por stop_sequence</t>
   </si>
   <si>
+    <t>Regularização temporal com intervalos positivos</t>
+  </si>
+  <si>
+    <t>Filtro técnico de qualidade para roteamento GTFS</t>
+  </si>
+  <si>
     <t>Associação de paradas à rede de caminhada</t>
   </si>
   <si>
@@ -1363,6 +1414,12 @@
     <t>_refine_stop_times_with_shape_geometry</t>
   </si>
   <si>
+    <t>_regularize_interpolated_stop_times</t>
+  </si>
+  <si>
+    <t>_build_routing_quality_filter</t>
+  </si>
+  <si>
     <t>_connect_stops_to_walk_network</t>
   </si>
   <si>
@@ -1444,6 +1501,12 @@
     <t>Usa a posição ordinal das paradas como fallback quando não existe uma base de distância válida</t>
   </si>
   <si>
+    <t>Redistribui o tempo entre pontos temporais originais preservando as âncoras publicadas e garantindo o intervalo mínimo configurado entre paradas consecutivas quando a alocação é matematicamente possível</t>
+  </si>
+  <si>
+    <t>Mantém a tabela completa para diagnóstico e cria separadamente um subconjunto roteável que retira viagens sem resumo temporal, com duração não positiva, regularização inviável ou velocidade implícita acima do limite técnico configurado</t>
+  </si>
+  <si>
     <t>Associa cada parada GTFS ao nó mais próximo da rede de caminhada e calcula distância e tempo do conector</t>
   </si>
   <si>
@@ -1654,6 +1717,12 @@
     <t>Preservação explícita de valores ausentes em diagnósticos temporais</t>
   </si>
   <si>
+    <t>Preservação dos horários-âncora na regularização temporal</t>
+  </si>
+  <si>
+    <t>Separação entre conexões completas e conexões roteáveis</t>
+  </si>
+  <si>
     <t>Remove espaços excedentes e normaliza campos textuais usados como identificadores e categorias</t>
   </si>
   <si>
@@ -1717,6 +1786,12 @@
     <t>Mantém viagens sem duração ou sem conexões como valores ausentes e evita classificá-las como duração não positiva ou como baixa quantidade de pontos temporais</t>
   </si>
   <si>
+    <t>Mantém os horários originais informados pelo produtor do GTFS e modifica somente os pontos temporais intermediários estimados</t>
+  </si>
+  <si>
+    <t>Preserva todas as conexões processadas para auditoria e cria um arquivo separado somente com viagens que atendem aos critérios técnicos de roteamento</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Métodos de limpeza</t>
   </si>
   <si>
@@ -1816,6 +1891,12 @@
     <t>transit_connections_processed.parquet</t>
   </si>
   <si>
+    <t>transit_connections_routable_processed.parquet</t>
+  </si>
+  <si>
+    <t>transit_trip_quality_processed.csv</t>
+  </si>
+  <si>
     <t>transit_topology_processed.parquet</t>
   </si>
   <si>
@@ -2002,6 +2083,12 @@
     <t>data/gtfs/transit_connections_processed.parquet</t>
   </si>
   <si>
+    <t>data/gtfs/transit_connections_routable_processed.parquet</t>
+  </si>
+  <si>
+    <t>data/gtfs/transit_trip_quality_processed.csv</t>
+  </si>
+  <si>
     <t>data/gtfs/transit_topology_processed.parquet</t>
   </si>
   <si>
@@ -2215,7 +2302,13 @@
     <t>Tabela tabular dos conectores entre paradas GTFS e nós da rede de caminhada</t>
   </si>
   <si>
-    <t>Tabela temporal de conexões entre paradas consecutivas de todas as viagens GTFS</t>
+    <t>Tabela temporal completa de conexões entre paradas consecutivas de todas as viagens GTFS processadas</t>
+  </si>
+  <si>
+    <t>Subconjunto das conexões GTFS cujas viagens atendem aos critérios técnicos de qualidade temporal usados pelo roteador</t>
+  </si>
+  <si>
+    <t>Diagnóstico por trip_id com critérios e motivos de inclusão ou exclusão da tabela de conexões roteáveis</t>
   </si>
   <si>
     <t>Resumo topológico das ligações entre pares direcionais de paradas por rota</t>
@@ -2795,7 +2888,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
@@ -2803,7 +2896,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
@@ -2819,7 +2912,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
@@ -2827,7 +2920,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2841,7 +2934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2852,7 +2945,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2877,13 +2970,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
@@ -2891,13 +2984,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
@@ -2905,13 +2998,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
@@ -2919,13 +3012,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
@@ -2933,13 +3026,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
@@ -2947,13 +3040,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="34" customHeight="1">
@@ -2961,13 +3054,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34" customHeight="1">
@@ -2975,13 +3068,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1">
@@ -2989,13 +3082,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34" customHeight="1">
@@ -3003,13 +3096,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34" customHeight="1">
@@ -3017,13 +3110,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="34" customHeight="1">
@@ -3031,13 +3124,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34" customHeight="1">
@@ -3045,13 +3138,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="34" customHeight="1">
@@ -3059,13 +3152,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34" customHeight="1">
@@ -3073,13 +3166,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="34" customHeight="1">
@@ -3087,13 +3180,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="34" customHeight="1">
@@ -3101,13 +3194,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" customHeight="1">
@@ -3115,13 +3208,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" customHeight="1">
@@ -3129,13 +3222,13 @@
         <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" customHeight="1">
@@ -3143,13 +3236,13 @@
         <v>39</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" customHeight="1">
@@ -3157,13 +3250,13 @@
         <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="34" customHeight="1">
@@ -3171,13 +3264,13 @@
         <v>41</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="34" customHeight="1">
@@ -3185,13 +3278,13 @@
         <v>42</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="34" customHeight="1">
@@ -3199,13 +3292,13 @@
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="34" customHeight="1">
@@ -3213,13 +3306,13 @@
         <v>44</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="34" customHeight="1">
@@ -3227,13 +3320,13 @@
         <v>45</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="34" customHeight="1">
@@ -3241,13 +3334,13 @@
         <v>46</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="34" customHeight="1">
@@ -3255,13 +3348,13 @@
         <v>47</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="34" customHeight="1">
@@ -3269,13 +3362,13 @@
         <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="34" customHeight="1">
@@ -3283,13 +3376,13 @@
         <v>49</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="34" customHeight="1">
@@ -3297,13 +3390,13 @@
         <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="34" customHeight="1">
@@ -3311,13 +3404,13 @@
         <v>51</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="34" customHeight="1">
@@ -3325,13 +3418,13 @@
         <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="34" customHeight="1">
@@ -3339,13 +3432,13 @@
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" customHeight="1">
@@ -3353,13 +3446,13 @@
         <v>54</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="34" customHeight="1">
@@ -3367,13 +3460,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="34" customHeight="1">
@@ -3381,13 +3474,13 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="34" customHeight="1">
@@ -3395,13 +3488,13 @@
         <v>57</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="34" customHeight="1">
@@ -3409,13 +3502,13 @@
         <v>58</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" customHeight="1">
@@ -3423,13 +3516,13 @@
         <v>59</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="34" customHeight="1">
@@ -3437,13 +3530,13 @@
         <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="34" customHeight="1">
@@ -3451,13 +3544,13 @@
         <v>61</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="34" customHeight="1">
@@ -3465,13 +3558,13 @@
         <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="34" customHeight="1">
@@ -3479,13 +3572,13 @@
         <v>63</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="34" customHeight="1">
@@ -3493,13 +3586,13 @@
         <v>64</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="34" customHeight="1">
@@ -3507,13 +3600,13 @@
         <v>65</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="34" customHeight="1">
@@ -3521,13 +3614,13 @@
         <v>66</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="34" customHeight="1">
@@ -3535,13 +3628,13 @@
         <v>67</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="34" customHeight="1">
@@ -3549,13 +3642,13 @@
         <v>68</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="34" customHeight="1">
@@ -3563,13 +3656,13 @@
         <v>69</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="34" customHeight="1">
@@ -3577,13 +3670,13 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="34" customHeight="1">
@@ -3591,13 +3684,13 @@
         <v>71</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="34" customHeight="1">
@@ -3605,13 +3698,13 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="34" customHeight="1">
@@ -3619,13 +3712,13 @@
         <v>73</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="34" customHeight="1">
@@ -3633,13 +3726,13 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="34" customHeight="1">
@@ -3647,13 +3740,13 @@
         <v>75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="34" customHeight="1">
@@ -3661,13 +3754,13 @@
         <v>76</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="34" customHeight="1">
@@ -3675,13 +3768,13 @@
         <v>77</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="34" customHeight="1">
@@ -3689,13 +3782,13 @@
         <v>78</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="34" customHeight="1">
@@ -3703,13 +3796,13 @@
         <v>79</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="34" customHeight="1">
@@ -3717,13 +3810,13 @@
         <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="34" customHeight="1">
@@ -3731,13 +3824,13 @@
         <v>81</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="34" customHeight="1">
@@ -3745,13 +3838,13 @@
         <v>82</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="34" customHeight="1">
@@ -3759,13 +3852,13 @@
         <v>83</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="34" customHeight="1">
@@ -3773,13 +3866,13 @@
         <v>84</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="34" customHeight="1">
@@ -3787,13 +3880,13 @@
         <v>85</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="34" customHeight="1">
@@ -3801,13 +3894,13 @@
         <v>86</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="34" customHeight="1">
@@ -3815,13 +3908,13 @@
         <v>87</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="34" customHeight="1">
@@ -3829,13 +3922,13 @@
         <v>88</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="34" customHeight="1">
@@ -3843,13 +3936,13 @@
         <v>89</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="34" customHeight="1">
@@ -3857,13 +3950,13 @@
         <v>90</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="34" customHeight="1">
@@ -3871,97 +3964,97 @@
         <v>91</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="34" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="34" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="34" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="34" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="34" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="34" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="34" customHeight="1">
@@ -3969,13 +4062,13 @@
         <v>97</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="34" customHeight="1">
@@ -3983,13 +4076,13 @@
         <v>98</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="34" customHeight="1">
@@ -3997,17 +4090,87 @@
         <v>99</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="34" customHeight="1">
+      <c r="A85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="34" customHeight="1">
+      <c r="A86" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="34" customHeight="1">
+      <c r="A87" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="34" customHeight="1">
+      <c r="A88" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="34" customHeight="1">
+      <c r="A89" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D84"/>
+  <autoFilter ref="A3:D89"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -4017,7 +4180,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.7109375" customWidth="1"/>
@@ -4029,7 +4192,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4050,1312 +4213,1346 @@
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3">
         <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B5" s="4">
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B7" s="4">
         <v>30000</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B9" s="4">
         <v>0.8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B13" s="4">
         <v>1.4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B15" s="4">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B16" s="3">
-        <v>1500</v>
+        <v>80</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>324</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B17" s="4">
-        <v>60</v>
+        <v>1500</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B18" s="3">
-        <v>14400</v>
+        <v>1500</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B19" s="4">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>312</v>
+        <v>128</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B20" s="3">
-        <v>28800</v>
+        <v>14400</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B21" s="4">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B22" s="3">
-        <v>0.20997644</v>
+        <v>28800</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B23" s="4"/>
+        <v>255</v>
+      </c>
+      <c r="B23" s="4">
+        <v>42</v>
+      </c>
       <c r="C23" s="4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B24" s="3">
-        <v>1913</v>
+        <v>0.20997644</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>313</v>
+        <v>132</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B25" s="4">
-        <v>0.6114473499999999</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>127</v>
+        <v>326</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B26" s="3">
         <v>1913</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B27" s="4">
-        <v>8245</v>
+        <v>0.6114473499999999</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>313</v>
+        <v>132</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B28" s="3">
-        <v>0.17857621</v>
+        <v>1913</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>127</v>
+        <v>326</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B29" s="4">
         <v>8245</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B30" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="B30" s="3">
+        <v>0.17857621</v>
+      </c>
       <c r="C30" s="3" t="s">
-        <v>313</v>
+        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B31" s="4">
-        <v>0.55</v>
+        <v>8245</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B32" s="3">
-        <v>0.12</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B33" s="4">
-        <v>0.03</v>
+        <v>0.55</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B34" s="3">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B35" s="4">
-        <v>6</v>
+        <v>0.03</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B36" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B37" s="4"/>
+        <v>269</v>
+      </c>
+      <c r="B37" s="4">
+        <v>6</v>
+      </c>
       <c r="C37" s="4" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B38" s="3"/>
+        <v>270</v>
+      </c>
+      <c r="B38" s="3">
+        <v>20</v>
+      </c>
       <c r="C38" s="3" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B39" s="4">
-        <v>0.1</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="B39" s="4"/>
       <c r="C39" s="4" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B40" s="3">
-        <v>0.09</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B41" s="4">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B42" s="3">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B43" s="4">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B44" s="3">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B45" s="4">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B46" s="3">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B47" s="4">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B48" s="3">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B49" s="4">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B50" s="3">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B51" s="4">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B52" s="3">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B53" s="4">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B54" s="3">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B55" s="4">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B56" s="3">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B57" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B58" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B59" s="4">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B60" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B61" s="4">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B62" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B63" s="4">
         <v>0.2</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B64" s="3">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="34" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B65" s="4">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B66" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="34" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B67" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B68" s="3">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="34" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B69" s="4">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B70" s="3">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="34" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B71" s="4">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="34" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B73" s="4">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="34" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B74" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="34" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B75" s="4">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="34" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B76" s="3">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="34" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B77" s="4">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="34" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B78" s="3">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="34" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B79" s="4">
         <v>0.1</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="34" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B80" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="34" customHeight="1">
+      <c r="A81" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B81" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="34" customHeight="1">
+      <c r="A82" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B82" s="3">
         <v>0.7</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>396</v>
+      <c r="C82" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E80"/>
+  <autoFilter ref="A3:E82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -5365,7 +5562,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -5375,7 +5572,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5385,7 +5582,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -5393,325 +5590,347 @@
     </row>
     <row r="4" spans="1:3" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>479</v>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="34" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="34" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C32"/>
+  <autoFilter ref="A3:C34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -5730,7 +5949,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -5744,154 +5963,154 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -5905,7 +6124,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -5914,7 +6133,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -5928,174 +6147,190 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>542</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>543</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>544</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>545</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>547</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>549</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>550</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>552</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>553</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>554</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>557</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>558</v>
+        <v>581</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>560</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>561</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="34" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="34" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>586</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B24"/>
+  <autoFilter ref="A3:B26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -6105,7 +6340,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -6118,7 +6353,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>766</v>
+        <v>797</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6132,42 +6367,42 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>563</v>
+        <v>588</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>566</v>
+        <v>591</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>567</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>630</v>
+        <v>657</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>702</v>
+        <v>731</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G4" s="3">
         <v>25498039</v>
@@ -6175,22 +6410,22 @@
     </row>
     <row r="5" spans="1:7" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>631</v>
+        <v>658</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>703</v>
+        <v>732</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G5" s="4">
         <v>54288508</v>
@@ -6198,22 +6433,22 @@
     </row>
     <row r="6" spans="1:7" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>632</v>
+        <v>659</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>704</v>
+        <v>733</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G6" s="3">
         <v>43443363</v>
@@ -6221,22 +6456,22 @@
     </row>
     <row r="7" spans="1:7" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>571</v>
+        <v>596</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>692</v>
+        <v>721</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>705</v>
+        <v>734</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G7" s="4">
         <v>25498039</v>
@@ -6244,22 +6479,22 @@
     </row>
     <row r="8" spans="1:7" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>572</v>
+        <v>597</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>634</v>
+        <v>661</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>693</v>
+        <v>722</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>706</v>
+        <v>735</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G8" s="3">
         <v>1671168</v>
@@ -6267,22 +6502,22 @@
     </row>
     <row r="9" spans="1:7" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>635</v>
+        <v>662</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>693</v>
+        <v>722</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>707</v>
+        <v>736</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G9" s="4">
         <v>1970176</v>
@@ -6290,22 +6525,22 @@
     </row>
     <row r="10" spans="1:7" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>574</v>
+        <v>599</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>694</v>
+        <v>723</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G10" s="3">
         <v>18419712</v>
@@ -6313,22 +6548,22 @@
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>637</v>
+        <v>664</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>694</v>
+        <v>723</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>709</v>
+        <v>738</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G11" s="4">
         <v>26136576</v>
@@ -6336,22 +6571,22 @@
     </row>
     <row r="12" spans="1:7" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>710</v>
+        <v>739</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G12" s="3">
         <v>7745077</v>
@@ -6359,22 +6594,22 @@
     </row>
     <row r="13" spans="1:7" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>639</v>
+        <v>666</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>711</v>
+        <v>740</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G13" s="4">
         <v>503</v>
@@ -6382,22 +6617,22 @@
     </row>
     <row r="14" spans="1:7" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>640</v>
+        <v>667</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>712</v>
+        <v>741</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G14" s="3">
         <v>5241</v>
@@ -6405,22 +6640,22 @@
     </row>
     <row r="15" spans="1:7" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>641</v>
+        <v>668</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>713</v>
+        <v>742</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G15" s="4">
         <v>16899</v>
@@ -6428,22 +6663,22 @@
     </row>
     <row r="16" spans="1:7" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>642</v>
+        <v>669</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>714</v>
+        <v>743</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G16" s="3">
         <v>279475</v>
@@ -6451,45 +6686,45 @@
     </row>
     <row r="17" spans="1:7" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>643</v>
+        <v>670</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>715</v>
+        <v>744</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G17" s="4">
-        <v>9517009</v>
+        <v>9488487</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>716</v>
+        <v>745</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G18" s="3">
         <v>11068</v>
@@ -6497,22 +6732,22 @@
     </row>
     <row r="19" spans="1:7" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>645</v>
+        <v>672</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>717</v>
+        <v>746</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G19" s="4">
         <v>14503</v>
@@ -6520,22 +6755,22 @@
     </row>
     <row r="20" spans="1:7" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>646</v>
+        <v>673</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>718</v>
+        <v>747</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G20" s="3">
         <v>11601</v>
@@ -6543,22 +6778,22 @@
     </row>
     <row r="21" spans="1:7" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>719</v>
+        <v>748</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G21" s="4">
         <v>921600</v>
@@ -6566,22 +6801,22 @@
     </row>
     <row r="22" spans="1:7" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>586</v>
+        <v>611</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>720</v>
+        <v>749</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G22" s="3">
         <v>4329472</v>
@@ -6589,64 +6824,64 @@
     </row>
     <row r="23" spans="1:7" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>721</v>
+        <v>750</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>588</v>
+        <v>613</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>722</v>
+        <v>751</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>589</v>
+        <v>614</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>651</v>
+        <v>678</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>723</v>
+        <v>752</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G25" s="4">
         <v>5040</v>
@@ -6654,68 +6889,68 @@
     </row>
     <row r="26" spans="1:7" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>590</v>
+        <v>615</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>724</v>
+        <v>753</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G26" s="3">
-        <v>1136</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>591</v>
+        <v>616</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>653</v>
+        <v>680</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>695</v>
+        <v>724</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>725</v>
+        <v>754</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G27" s="4">
-        <v>765</v>
+        <v>932</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>726</v>
+        <v>755</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G28" s="3">
         <v>1069056</v>
@@ -6723,22 +6958,22 @@
     </row>
     <row r="29" spans="1:7" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>655</v>
+        <v>682</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>727</v>
+        <v>756</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G29" s="4">
         <v>187087</v>
@@ -6746,834 +6981,880 @@
     </row>
     <row r="30" spans="1:7" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>594</v>
+        <v>619</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>728</v>
+        <v>757</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G30" s="3">
-        <v>50224012</v>
+        <v>49996766</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>595</v>
+        <v>620</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>657</v>
+        <v>684</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>729</v>
+        <v>758</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G31" s="4">
-        <v>228006</v>
+        <v>47656187</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>696</v>
+        <v>116</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>730</v>
+        <v>759</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G32" s="3">
-        <v>3123</v>
+        <v>7427833</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>597</v>
+        <v>622</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>659</v>
+        <v>686</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>696</v>
+        <v>725</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>731</v>
+        <v>760</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G33" s="4">
-        <v>840</v>
+        <v>226715</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>660</v>
+        <v>687</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>732</v>
+        <v>761</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G34" s="3">
-        <v>227102</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>599</v>
+        <v>624</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>661</v>
+        <v>688</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>697</v>
+        <v>725</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>733</v>
+        <v>762</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G35" s="4">
-        <v>224907</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>662</v>
+        <v>689</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>697</v>
+        <v>726</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>734</v>
+        <v>763</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G36" s="3">
-        <v>451839</v>
+        <v>227102</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>601</v>
+        <v>626</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>735</v>
+        <v>764</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G37" s="4">
-        <v>1288420</v>
+        <v>224907</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>602</v>
+        <v>627</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>664</v>
+        <v>691</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>698</v>
+        <v>726</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>736</v>
+        <v>765</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G38" s="3">
-        <v>1314652</v>
+        <v>451839</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>665</v>
+        <v>692</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>698</v>
+        <v>727</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>737</v>
+        <v>766</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G39" s="4">
-        <v>2602915</v>
+        <v>1288420</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>604</v>
+        <v>629</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>105</v>
+        <v>727</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>738</v>
+        <v>767</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G40" s="3">
-        <v>2109747</v>
+        <v>1314652</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>105</v>
+        <v>727</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>739</v>
+        <v>768</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G41" s="4">
-        <v>2106524</v>
+        <v>2602915</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>606</v>
+        <v>631</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>668</v>
+        <v>695</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>740</v>
+        <v>769</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G42" s="3">
-        <v>4216067</v>
+        <v>2109747</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>669</v>
+        <v>696</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>741</v>
+        <v>770</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G43" s="4">
-        <v>15617568</v>
+        <v>2106524</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>742</v>
+        <v>771</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G44" s="3">
-        <v>556</v>
+        <v>4216067</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>743</v>
+        <v>772</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G45" s="4">
-        <v>525</v>
+        <v>15617568</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>744</v>
+        <v>773</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G46" s="3">
-        <v>17707008</v>
+        <v>556</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>673</v>
+        <v>700</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G47" s="4">
-        <v>714918</v>
+        <v>525</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>746</v>
+        <v>775</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G48" s="3">
-        <v>745255</v>
+        <v>17707008</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>747</v>
+        <v>776</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G49" s="4">
-        <v>1459825</v>
+        <v>714918</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>676</v>
+        <v>703</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>748</v>
+        <v>777</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G50" s="3">
-        <v>20062208</v>
+        <v>745255</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>615</v>
+        <v>640</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>749</v>
+        <v>778</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G51" s="4">
-        <v>20447232</v>
+        <v>1459825</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>616</v>
+        <v>641</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>699</v>
+        <v>112</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>750</v>
+        <v>779</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G52" s="3">
-        <v>2492663</v>
+        <v>20062208</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>617</v>
+        <v>642</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>699</v>
+        <v>112</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>751</v>
+        <v>780</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G53" s="4">
-        <v>704</v>
+        <v>20447232</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>618</v>
+        <v>643</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>680</v>
+        <v>707</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>699</v>
+        <v>728</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>752</v>
+        <v>781</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G54" s="3">
-        <v>23400448</v>
+        <v>2492663</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>681</v>
+        <v>708</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>700</v>
+        <v>728</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>753</v>
+        <v>782</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G55" s="4">
-        <v>1094788</v>
+        <v>704</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>682</v>
+        <v>709</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>700</v>
+        <v>728</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>754</v>
+        <v>783</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G56" s="3">
-        <v>870164</v>
+        <v>23400448</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>621</v>
+        <v>646</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>700</v>
+        <v>729</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G57" s="4">
-        <v>1095579</v>
+        <v>1094788</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>622</v>
+        <v>647</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>700</v>
+        <v>729</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>756</v>
+        <v>785</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G58" s="3">
-        <v>877549</v>
+        <v>870164</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>685</v>
+        <v>712</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>700</v>
+        <v>729</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>757</v>
+        <v>786</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G59" s="4">
-        <v>940952</v>
+        <v>1095579</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>686</v>
+        <v>713</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>700</v>
+        <v>729</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>758</v>
+        <v>787</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G60" s="3">
-        <v>854357</v>
+        <v>877549</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>687</v>
+        <v>714</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>700</v>
+        <v>729</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>759</v>
+        <v>788</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G61" s="4">
-        <v>542</v>
+        <v>940952</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>112</v>
+        <v>729</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>760</v>
+        <v>789</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G62" s="3">
-        <v>28018</v>
+        <v>854357</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>114</v>
+        <v>729</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>761</v>
+        <v>790</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G63" s="4">
-        <v>5915237</v>
+        <v>542</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>701</v>
+        <v>118</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G64" s="3">
-        <v>27138</v>
+        <v>23749</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="34" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>701</v>
+        <v>116</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>765</v>
+        <v>796</v>
       </c>
       <c r="G65" s="4">
-        <v>74339</v>
+        <v>6348715</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="34" customHeight="1">
+      <c r="A66" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="G66" s="3">
+        <v>28579</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="34" customHeight="1">
+      <c r="A67" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="G67" s="4">
+        <v>80203</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G65"/>
+  <autoFilter ref="A3:G67"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/outputs/metadados_piloto.xlsx
+++ b/outputs/metadados_piloto.xlsx
@@ -16,20 +16,20 @@
     <sheet name="Arquivos gerados" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resumo!$A$3:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="935">
   <si>
     <t>campo</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Piloto computacional de mobilidade urbana, diferenciação socioespacial e entropia socioeconômica de trajetórias</t>
   </si>
   <si>
-    <t>2026-09-28T08:30:55.189767+00:00</t>
+    <t>2026-09-28T12:46:33.726833+00:00</t>
   </si>
   <si>
     <t>português</t>
@@ -148,6 +148,15 @@
     <t>modal_edge_id</t>
   </si>
   <si>
+    <t>mapping_mode</t>
+  </si>
+  <si>
+    <t>leg_mode</t>
+  </si>
+  <si>
+    <t>transit_leg</t>
+  </si>
+  <si>
     <t>edge_length_m</t>
   </si>
   <si>
@@ -226,6 +235,24 @@
     <t>delta_n_passages</t>
   </si>
   <si>
+    <t>route_to_od_ratio</t>
+  </si>
+  <si>
+    <t>direct_outlier</t>
+  </si>
+  <si>
+    <t>analysis_included</t>
+  </si>
+  <si>
+    <t>analysis_exclusion_reason</t>
+  </si>
+  <si>
+    <t>direct_spatial_mapping_failure</t>
+  </si>
+  <si>
+    <t>analysis_excluded_spatial_mapping</t>
+  </si>
+  <si>
     <t>sufficient_flow_both</t>
   </si>
   <si>
@@ -346,6 +373,21 @@
     <t>egress_walk_time_s</t>
   </si>
   <si>
+    <t>transit_service_date</t>
+  </si>
+  <si>
+    <t>transit_departure_time_s</t>
+  </si>
+  <si>
+    <t>transit_in_vehicle_distance_m</t>
+  </si>
+  <si>
+    <t>transit_connection_ids</t>
+  </si>
+  <si>
+    <t>shape_coverage_pct</t>
+  </si>
+  <si>
     <t>agente</t>
   </si>
   <si>
@@ -364,6 +406,9 @@
     <t>harmonização</t>
   </si>
   <si>
+    <t>trajetória multimodal</t>
+  </si>
+  <si>
     <t>estatística por segmento</t>
   </si>
   <si>
@@ -376,6 +421,15 @@
     <t>comparação de cenários</t>
   </si>
   <si>
+    <t>controle de outliers</t>
+  </si>
+  <si>
+    <t>controle analítico</t>
+  </si>
+  <si>
+    <t>controle de espacialização transit</t>
+  </si>
+  <si>
     <t>GTFS</t>
   </si>
   <si>
@@ -391,6 +445,9 @@
     <t>diagnóstico de transporte coletivo</t>
   </si>
   <si>
+    <t>harmonização do transporte coletivo</t>
+  </si>
+  <si>
     <t>identificador</t>
   </si>
   <si>
@@ -451,6 +508,9 @@
     <t>passagens</t>
   </si>
   <si>
+    <t>razão adimensional</t>
+  </si>
+  <si>
     <t>código GTFS</t>
   </si>
   <si>
@@ -475,6 +535,12 @@
     <t>s/conexão</t>
   </si>
   <si>
+    <t>lista de identificadores</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>Identificador único do agente sintético</t>
   </si>
   <si>
@@ -529,7 +595,16 @@
     <t>Chave da aresta em um MultiDiGraph</t>
   </si>
   <si>
-    <t>Identificador estável de uma aresta dentro de uma rede modal</t>
+    <t>Identificador estável de uma aresta dentro de uma rede modal ou de uma conexão GTFS usada na trajetória</t>
+  </si>
+  <si>
+    <t>Rede ou fonte geométrica usada para associar a passagem ao analysis_segment_id sem alterar o modo principal da viagem</t>
+  </si>
+  <si>
+    <t>Modo efetivamente usado no trecho da trajetória, distinguindo caminhada de acesso ou egresso e trecho embarcado</t>
+  </si>
+  <si>
+    <t>Classifica o trecho de uma viagem transit como access_walk, in_vehicle ou egress_walk</t>
   </si>
   <si>
     <t>Comprimento da aresta modal</t>
@@ -610,6 +685,24 @@
     <t>Diferença no número de passagens entre differentiated e baseline</t>
   </si>
   <si>
+    <t>Razão entre a distância roteada e a distância euclidiana origem-destino usada para diagnosticar trajetórias excessivamente circuitosas</t>
+  </si>
+  <si>
+    <t>Indica que a viagem transit excede a cerca externa da distância roteada ou combina circuity extrema com distância roteada acima do terceiro quartil</t>
+  </si>
+  <si>
+    <t>Indica se o agente permanece na análise de trajetórias e H_soc após o controle pareado de outliers</t>
+  </si>
+  <si>
+    <t>Registra os motivos cumulativos pelos quais o agente é retirado da análise de trajetórias, incluindo outlier e falha de espacialização transit</t>
+  </si>
+  <si>
+    <t>Indica que o agente usa ao menos uma conexão GTFS sem correspondência válida na camada física comum</t>
+  </si>
+  <si>
+    <t>Indica que o agente foi retirado da análise espacial por falha direta de espacialização ou para preservar a exclusão pareada entre cenários</t>
+  </si>
+  <si>
     <t>Indica se o fluxo mínimo para interpretação é atingido nos dois cenários</t>
   </si>
   <si>
@@ -733,6 +826,21 @@
     <t>Tempo total de caminhada entre a parada de desembarque e o destino</t>
   </si>
   <si>
+    <t>Data histórica de serviço GTFS usada para rotear o agente no piloto</t>
+  </si>
+  <si>
+    <t>Horário fixo de partida usado no roteamento transit do piloto técnico</t>
+  </si>
+  <si>
+    <t>Distância acumulada ao longo dos shapes das conexões GTFS embarcadas pelo agente</t>
+  </si>
+  <si>
+    <t>Sequência de connection_id GTFS usada pela rota transit do agente</t>
+  </si>
+  <si>
+    <t>Percentual do trecho de shape de uma conexão GTFS coberto pelos buffers dos segmentos físicos associados</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Variáveis</t>
   </si>
   <si>
@@ -763,9 +871,21 @@
     <t>analysis.segment_statistics.flow_thresholds</t>
   </si>
   <si>
+    <t>analysis.trip_outliers.iqr_multiplier</t>
+  </si>
+  <si>
+    <t>analysis.trip_outliers.min_sample_size</t>
+  </si>
+  <si>
+    <t>analysis.trip_outliers.paired_exclusion</t>
+  </si>
+  <si>
     <t>routing.implemented_modes</t>
   </si>
   <si>
+    <t>routing.choice_modes</t>
+  </si>
+  <si>
     <t>transit.network.walk_speed_m_s</t>
   </si>
   <si>
@@ -790,6 +910,33 @@
     <t>transit.routing.max_total_travel_time_s</t>
   </si>
   <si>
+    <t>transit.routing.pilot_departure_time_s</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.primary.tolerance_m</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.primary.min_coverage</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.primary.max_angle_difference_deg</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.fallback.tolerance_m</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.fallback.min_coverage</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.fallback.max_angle_difference_deg</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.unmatched_policy</t>
+  </si>
+  <si>
+    <t>transit.spatial_mapping.paired_exclusion</t>
+  </si>
+  <si>
     <t>transit.routing.diagnostics.sample_size</t>
   </si>
   <si>
@@ -985,9 +1132,15 @@
     <t>walk | bike | car</t>
   </si>
   <si>
+    <t>walk | bike | car | transit</t>
+  </si>
+  <si>
     <t>max_scheduled_trips</t>
   </si>
   <si>
+    <t>exclude_agent_paired</t>
+  </si>
+  <si>
     <t>agentes</t>
   </si>
   <si>
@@ -997,6 +1150,12 @@
     <t>CRS</t>
   </si>
   <si>
+    <t>multiplicador do IQR</t>
+  </si>
+  <si>
+    <t>viagens transit</t>
+  </si>
+  <si>
     <t>categorias</t>
   </si>
   <si>
@@ -1006,6 +1165,9 @@
     <t>km/h</t>
   </si>
   <si>
+    <t>graus</t>
+  </si>
+  <si>
     <t>viagens OD</t>
   </si>
   <si>
@@ -1045,7 +1207,19 @@
     <t>Limiares preservados para análise de sensibilidade do suporte amostral por segmento</t>
   </si>
   <si>
-    <t>Modos com roteamento viário atualmente integrado ao run_pilot</t>
+    <t>Multiplicador usado na cerca externa superior de Tukey aplicada às métricas de distância e circuity</t>
+  </si>
+  <si>
+    <t>Quantidade mínima de viagens elegíveis nos dois cenários combinados para ativar o filtro de outliers</t>
+  </si>
+  <si>
+    <t>Indica se um agent_id identificado como outlier em um cenário também é retirado da análise espacial no outro cenário</t>
+  </si>
+  <si>
+    <t>Modos com grafo OSM carregado diretamente no run_pilot</t>
+  </si>
+  <si>
+    <t>Modos disponíveis para a escolha modal dos agentes no piloto integrado</t>
   </si>
   <si>
     <t>Velocidade provisória usada para converter o conector parada-rede de caminhada em tempo</t>
@@ -1072,6 +1246,33 @@
     <t>Horizonte máximo provisório considerado em uma consulta de transporte coletivo</t>
   </si>
   <si>
+    <t>Horário fixo adotado para o roteamento transit dos agentes no piloto técnico</t>
+  </si>
+  <si>
+    <t>Tolerância da etapa primária usada para associar trechos GTFS aos segmentos físicos com suporte da rede car</t>
+  </si>
+  <si>
+    <t>Cobertura mínima por segmento ou por trecho de shape exigida na etapa primária do mapeamento GTFS</t>
+  </si>
+  <si>
+    <t>Diferença angular local máxima permitida na etapa primária do mapeamento GTFS</t>
+  </si>
+  <si>
+    <t>Tolerância espacial da etapa de fallback aplicada somente às conexões ainda não mapeadas</t>
+  </si>
+  <si>
+    <t>Cobertura mínima por segmento ou por trecho de shape na etapa de fallback da rede física completa</t>
+  </si>
+  <si>
+    <t>Diferença angular local máxima permitida na etapa de fallback</t>
+  </si>
+  <si>
+    <t>Política aplicada quando conexões GTFS usadas não encontram correspondência na camada física comum</t>
+  </si>
+  <si>
+    <t>Indica se a falha espacial de um agente em um cenário também retira o mesmo agent_id da análise espacial no outro cenário</t>
+  </si>
+  <si>
     <t>Quantidade de pares origem-destino usada no diagnóstico técnico do roteador temporal</t>
   </si>
   <si>
@@ -1366,6 +1567,30 @@
     <t>Diagnóstico temporal por viagem GTFS</t>
   </si>
   <si>
+    <t>Roteamento integrado do piloto</t>
+  </si>
+  <si>
+    <t>Representação multimodal da trajetória transit</t>
+  </si>
+  <si>
+    <t>Extração parcial do shape GTFS</t>
+  </si>
+  <si>
+    <t>Mapeamento geométrico de transit para segmentos físicos</t>
+  </si>
+  <si>
+    <t>Mapeamento espacial hierárquico do transporte coletivo</t>
+  </si>
+  <si>
+    <t>Recuperação ordenada da posição de paradas no shape</t>
+  </si>
+  <si>
+    <t>Filtro pareado de outliers de trajetórias transit</t>
+  </si>
+  <si>
+    <t>Exclusão pareada por falha de espacialização transit</t>
+  </si>
+  <si>
     <t>generate_population</t>
   </si>
   <si>
@@ -1441,6 +1666,30 @@
     <t>build_trip_temporal_quality</t>
   </si>
   <si>
+    <t>route_pilot_agents</t>
+  </si>
+  <si>
+    <t>build_transit_edge_usage</t>
+  </si>
+  <si>
+    <t>build_used_transit_connection_geometries</t>
+  </si>
+  <si>
+    <t>map_transit_connections_to_analysis_segments</t>
+  </si>
+  <si>
+    <t>map_transit_connections_hierarchically</t>
+  </si>
+  <si>
+    <t>_forward_stop_positions</t>
+  </si>
+  <si>
+    <t>apply_paired_transit_outlier_filter</t>
+  </si>
+  <si>
+    <t>apply_paired_transit_spatial_exclusions</t>
+  </si>
+  <si>
     <t>Gera agentes sintéticos preservando as participações configuradas para os grupos de renda</t>
   </si>
   <si>
@@ -1534,6 +1783,30 @@
     <t>Resume por trip_id a quantidade de pontos temporais originais, a duração programada, a incidência de conexões de duração zero e a velocidade implícita pelo comprimento do shape</t>
   </si>
   <si>
+    <t>Encaminha walk, bike e car para as redes OSM e transit para o roteador temporal GTFS preservando uma interface comum no agente</t>
+  </si>
+  <si>
+    <t>Decompõe uma viagem transit em caminhada de acesso, conexões embarcadas e caminhada de egresso preservando transit como modo principal da viagem</t>
+  </si>
+  <si>
+    <t>Recorta a geometria do shape somente entre as posições das paradas consecutivas efetivamente usadas pelas conexões selecionadas</t>
+  </si>
+  <si>
+    <t>Associa trechos GTFS usados aos segmentos físicos usando proximidade, cobertura do segmento ou do shape e compatibilidade da orientação local</t>
+  </si>
+  <si>
+    <t>Procura primeiro correspondência em segmentos com suporte da rede car e aplica uma segunda etapa na rede física completa somente às conexões ainda não mapeadas</t>
+  </si>
+  <si>
+    <t>Seleciona projeções sucessivas das paradas ao longo do shape quando as posições processadas estão ausentes, iguais ou decrescentes, preservando a ordem do deslocamento</t>
+  </si>
+  <si>
+    <t>Calcula limites robustos com os dois cenários combinados, identifica distância extrema ou circuity extrema acompanhada de rota longa e propaga a exclusão ao mesmo agent_id nos dois cenários</t>
+  </si>
+  <si>
+    <t>Identifica agentes cujas conexões GTFS usadas não possuem correspondência na camada física comum e retira o mesmo agent_id da análise espacial nos dois cenários quando o pareamento está habilitado</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Métodos de análise</t>
   </si>
   <si>
@@ -1594,6 +1867,18 @@
     <t>Participação de conexões de duração zero por viagem</t>
   </si>
   <si>
+    <t>Cobertura geométrica do shape</t>
+  </si>
+  <si>
+    <t>Taxa de sucesso do mapeamento espacial transit</t>
+  </si>
+  <si>
+    <t>Cerca externa superior de Tukey</t>
+  </si>
+  <si>
+    <t>Circuity da viagem</t>
+  </si>
+  <si>
     <t>Quantifica agentes, viagens, arestas, segmentos, paradas, rotas, shapes e demais unidades discretas</t>
   </si>
   <si>
@@ -1651,6 +1936,18 @@
     <t>Mede a proporção de conexões consecutivas com tempo veicular igual a zero dentro de cada trip_id</t>
   </si>
   <si>
+    <t>Mede o percentual do trecho GTFS usado que fica coberto pelos segmentos físicos associados dentro da tolerância espacial</t>
+  </si>
+  <si>
+    <t>Calcula a proporção das conexões GTFS usadas que possuem geometria válida e correspondência com pelo menos um analysis_segment_id</t>
+  </si>
+  <si>
+    <t>Calcula Q3 mais três vezes o intervalo interquartil por padrão para identificar valores extremos sem depender da média ou do desvio padrão</t>
+  </si>
+  <si>
+    <t>Relaciona a distância roteada à distância euclidiana origem-destino para distinguir rotas longas de trajetórias desproporcionalmente circuitosas</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Estatísticas</t>
   </si>
   <si>
@@ -1723,6 +2020,27 @@
     <t>Separação entre conexões completas e conexões roteáveis</t>
   </si>
   <si>
+    <t>Separação entre modo da viagem e modo de harmonização</t>
+  </si>
+  <si>
+    <t>Validação de cobertura espacial das conexões GTFS usadas</t>
+  </si>
+  <si>
+    <t>Fallback de projeção ordenada das paradas no shape</t>
+  </si>
+  <si>
+    <t>Cobertura bidirecional no mapeamento GTFS</t>
+  </si>
+  <si>
+    <t>Exclusão pareada de outliers de trajetória</t>
+  </si>
+  <si>
+    <t>Critério conservador de distância e circuity</t>
+  </si>
+  <si>
+    <t>Exclusão pareada de falhas de espacialização transit</t>
+  </si>
+  <si>
     <t>Remove espaços excedentes e normaliza campos textuais usados como identificadores e categorias</t>
   </si>
   <si>
@@ -1792,6 +2110,27 @@
     <t>Preserva todas as conexões processadas para auditoria e cria um arquivo separado somente com viagens que atendem aos critérios técnicos de roteamento</t>
   </si>
   <si>
+    <t>Preserva transit como modo principal do agente enquanto usa walk para mapear os trechos pedonais de acesso e egresso à camada física comum</t>
+  </si>
+  <si>
+    <t>Interrompe o piloto quando uma conexão transit usada por agente não encontra correspondência na camada física comum após as etapas primária e de fallback e evita omissão silenciosa no H_soc</t>
+  </si>
+  <si>
+    <t>Recupera trechos GTFS com progresso geométrico não positivo por meio de projeções sucessivas das paradas e registra explicitamente position_method e distâncias de snap</t>
+  </si>
+  <si>
+    <t>Aceita uma correspondência quando o segmento físico ou o trecho de shape atinge a cobertura mínima configurada, reduzindo rejeições artificiais de conexões curtas contidas em segmentos mais longos</t>
+  </si>
+  <si>
+    <t>Remove a trajetória do cálculo espacial sem apagar o registro original do agente e aplica a mesma exclusão ao agent_id correspondente no outro cenário para preservar comparabilidade</t>
+  </si>
+  <si>
+    <t>Exclui distância roteada acima da cerca externa ou circuity acima da cerca externa quando a rota também está acima do terceiro quartil, evitando excluir viagens curtas apenas por apresentarem razão elevada</t>
+  </si>
+  <si>
+    <t>Retira da análise de H_soc toda a trajetória do agente quando ao menos uma conexão GTFS usada não pode ser associada a analysis_segment_id e aplica a mesma retirada ao agent_id correspondente no outro cenário</t>
+  </si>
+  <si>
     <t>Metadados do piloto — Métodos de limpeza</t>
   </si>
   <si>
@@ -1996,6 +2335,30 @@
     <t>gtfs_trip_temporal_quality.csv</t>
   </si>
   <si>
+    <t>transit_connection_to_analysis_segment.csv</t>
+  </si>
+  <si>
+    <t>transit_connection_geometry_diagnostics.csv</t>
+  </si>
+  <si>
+    <t>transit_connection_match_diagnostics.csv</t>
+  </si>
+  <si>
+    <t>transit_spatial_match_report.csv</t>
+  </si>
+  <si>
+    <t>outlier_exclusions.csv</t>
+  </si>
+  <si>
+    <t>outlier_filter_summary.csv</t>
+  </si>
+  <si>
+    <t>transit_spatial_exclusions.csv</t>
+  </si>
+  <si>
+    <t>transit_spatial_exclusion_summary.csv</t>
+  </si>
+  <si>
     <t>metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -2188,6 +2551,30 @@
     <t>outputs/pilot/gtfs_trip_temporal_quality.csv</t>
   </si>
   <si>
+    <t>outputs/pilot/transit_connection_to_analysis_segment.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/transit_connection_geometry_diagnostics.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/transit_connection_match_diagnostics.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/transit_spatial_match_report.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/outlier_exclusions.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/outlier_filter_summary.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/transit_spatial_exclusions.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/transit_spatial_exclusion_summary.csv</t>
+  </si>
+  <si>
     <t>outputs/metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -2408,6 +2795,30 @@
   </si>
   <si>
     <t>Diagnóstico por trip_id com duração programada, pontos temporais originais, conexões de duração zero e velocidade implícita pelo shape</t>
+  </si>
+  <si>
+    <t>Mapeamento das conexões GTFS usadas pelos agentes para os segmentos físicos comuns do piloto</t>
+  </si>
+  <si>
+    <t>Diagnóstico da disponibilidade e validade da geometria parcial de cada conexão GTFS usada</t>
+  </si>
+  <si>
+    <t>Diagnóstico de quantidade de segmentos associados e cobertura geométrica por conexão GTFS usada</t>
+  </si>
+  <si>
+    <t>Resumo da cobertura e do sucesso do mapeamento espacial das conexões GTFS usadas</t>
+  </si>
+  <si>
+    <t>Registro auditável de cada cenário e agente retirado da análise de trajetórias por outlier transit direto ou exclusão pareada</t>
+  </si>
+  <si>
+    <t>Resumo do método, quartis, cercas externas e quantidade de outliers identificados no piloto</t>
+  </si>
+  <si>
+    <t>Registro por cenário e agente retirado da análise por conexões GTFS sem correspondência espacial, incluindo rotas e viagens afetadas</t>
+  </si>
+  <si>
+    <t>Resumo da quantidade de conexões sem correspondência e de agentes afetados pela exclusão espacial pareada</t>
   </si>
   <si>
     <t>Planilha consolidada com variáveis, parâmetros, métodos, estatísticas, limpeza e arquivos do piloto</t>
@@ -2888,7 +3299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
@@ -2896,7 +3307,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
@@ -2904,7 +3315,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
@@ -2912,7 +3323,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
@@ -2920,7 +3331,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2934,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2945,7 +3356,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2970,13 +3381,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1">
@@ -2984,13 +3395,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34" customHeight="1">
@@ -2998,13 +3409,13 @@
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="34" customHeight="1">
@@ -3012,13 +3423,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34" customHeight="1">
@@ -3026,13 +3437,13 @@
         <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="34" customHeight="1">
@@ -3040,13 +3451,13 @@
         <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="34" customHeight="1">
@@ -3054,13 +3465,13 @@
         <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34" customHeight="1">
@@ -3068,13 +3479,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1">
@@ -3082,13 +3493,13 @@
         <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="34" customHeight="1">
@@ -3096,13 +3507,13 @@
         <v>29</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="34" customHeight="1">
@@ -3110,13 +3521,13 @@
         <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="34" customHeight="1">
@@ -3124,13 +3535,13 @@
         <v>31</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34" customHeight="1">
@@ -3138,13 +3549,13 @@
         <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="34" customHeight="1">
@@ -3152,13 +3563,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34" customHeight="1">
@@ -3166,13 +3577,13 @@
         <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="34" customHeight="1">
@@ -3180,13 +3591,13 @@
         <v>35</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="34" customHeight="1">
@@ -3194,13 +3605,13 @@
         <v>36</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" customHeight="1">
@@ -3208,13 +3619,13 @@
         <v>37</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="34" customHeight="1">
@@ -3222,13 +3633,13 @@
         <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="34" customHeight="1">
@@ -3236,13 +3647,13 @@
         <v>39</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="34" customHeight="1">
@@ -3250,13 +3661,13 @@
         <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="34" customHeight="1">
@@ -3264,13 +3675,13 @@
         <v>41</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="34" customHeight="1">
@@ -3278,13 +3689,13 @@
         <v>42</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="34" customHeight="1">
@@ -3292,13 +3703,13 @@
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="34" customHeight="1">
@@ -3306,13 +3717,13 @@
         <v>44</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="34" customHeight="1">
@@ -3320,13 +3731,13 @@
         <v>45</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="34" customHeight="1">
@@ -3334,13 +3745,13 @@
         <v>46</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="34" customHeight="1">
@@ -3348,13 +3759,13 @@
         <v>47</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="34" customHeight="1">
@@ -3362,13 +3773,13 @@
         <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="34" customHeight="1">
@@ -3376,13 +3787,13 @@
         <v>49</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="34" customHeight="1">
@@ -3390,13 +3801,13 @@
         <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="34" customHeight="1">
@@ -3404,13 +3815,13 @@
         <v>51</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="34" customHeight="1">
@@ -3418,13 +3829,13 @@
         <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="34" customHeight="1">
@@ -3432,13 +3843,13 @@
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="34" customHeight="1">
@@ -3446,13 +3857,13 @@
         <v>54</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="34" customHeight="1">
@@ -3460,13 +3871,13 @@
         <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="34" customHeight="1">
@@ -3474,13 +3885,13 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="34" customHeight="1">
@@ -3488,13 +3899,13 @@
         <v>57</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="34" customHeight="1">
@@ -3502,13 +3913,13 @@
         <v>58</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="34" customHeight="1">
@@ -3516,13 +3927,13 @@
         <v>59</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="34" customHeight="1">
@@ -3530,13 +3941,13 @@
         <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="34" customHeight="1">
@@ -3544,13 +3955,13 @@
         <v>61</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="34" customHeight="1">
@@ -3558,13 +3969,13 @@
         <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="34" customHeight="1">
@@ -3572,13 +3983,13 @@
         <v>63</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="34" customHeight="1">
@@ -3586,13 +3997,13 @@
         <v>64</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="34" customHeight="1">
@@ -3600,13 +4011,13 @@
         <v>65</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="34" customHeight="1">
@@ -3614,13 +4025,13 @@
         <v>66</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="34" customHeight="1">
@@ -3628,13 +4039,13 @@
         <v>67</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="34" customHeight="1">
@@ -3642,13 +4053,13 @@
         <v>68</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="34" customHeight="1">
@@ -3656,13 +4067,13 @@
         <v>69</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="34" customHeight="1">
@@ -3670,13 +4081,13 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="34" customHeight="1">
@@ -3684,13 +4095,13 @@
         <v>71</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="34" customHeight="1">
@@ -3698,13 +4109,13 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="34" customHeight="1">
@@ -3712,13 +4123,13 @@
         <v>73</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="34" customHeight="1">
@@ -3726,13 +4137,13 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="34" customHeight="1">
@@ -3740,13 +4151,13 @@
         <v>75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="34" customHeight="1">
@@ -3754,13 +4165,13 @@
         <v>76</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="34" customHeight="1">
@@ -3768,13 +4179,13 @@
         <v>77</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="34" customHeight="1">
@@ -3782,13 +4193,13 @@
         <v>78</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="34" customHeight="1">
@@ -3796,13 +4207,13 @@
         <v>79</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="34" customHeight="1">
@@ -3810,13 +4221,13 @@
         <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="34" customHeight="1">
@@ -3824,13 +4235,13 @@
         <v>81</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="34" customHeight="1">
@@ -3838,13 +4249,13 @@
         <v>82</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="34" customHeight="1">
@@ -3852,13 +4263,13 @@
         <v>83</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="34" customHeight="1">
@@ -3866,13 +4277,13 @@
         <v>84</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="34" customHeight="1">
@@ -3880,13 +4291,13 @@
         <v>85</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="34" customHeight="1">
@@ -3894,13 +4305,13 @@
         <v>86</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="34" customHeight="1">
@@ -3908,13 +4319,13 @@
         <v>87</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="34" customHeight="1">
@@ -3922,13 +4333,13 @@
         <v>88</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="34" customHeight="1">
@@ -3936,13 +4347,13 @@
         <v>89</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="34" customHeight="1">
@@ -3950,13 +4361,13 @@
         <v>90</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="34" customHeight="1">
@@ -3964,13 +4375,13 @@
         <v>91</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="34" customHeight="1">
@@ -3978,13 +4389,13 @@
         <v>92</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="34" customHeight="1">
@@ -3992,13 +4403,13 @@
         <v>93</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="34" customHeight="1">
@@ -4006,13 +4417,13 @@
         <v>94</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="34" customHeight="1">
@@ -4020,13 +4431,13 @@
         <v>95</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="34" customHeight="1">
@@ -4034,143 +4445,339 @@
         <v>96</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="34" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="34" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="34" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="34" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="34" customHeight="1">
       <c r="A85" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="34" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="34" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="34" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="34" customHeight="1">
       <c r="A89" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B89" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="34" customHeight="1">
+      <c r="A90" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="34" customHeight="1">
+      <c r="A91" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="34" customHeight="1">
+      <c r="A92" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="34" customHeight="1">
+      <c r="A93" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="34" customHeight="1">
+      <c r="A94" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="34" customHeight="1">
+      <c r="A95" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="34" customHeight="1">
+      <c r="A96" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="34" customHeight="1">
+      <c r="A97" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="34" customHeight="1">
+      <c r="A98" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="34" customHeight="1">
+      <c r="A99" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="34" customHeight="1">
+      <c r="A100" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="34" customHeight="1">
+      <c r="A101" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="34" customHeight="1">
+      <c r="A102" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="34" customHeight="1">
+      <c r="A103" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>233</v>
+      <c r="B103" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D89"/>
+  <autoFilter ref="A3:D103"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -4180,7 +4787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.7109375" customWidth="1"/>
@@ -4192,7 +4799,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>479</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4213,1346 +4820,1567 @@
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="B4" s="3">
         <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>330</v>
+        <v>384</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>409</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="B5" s="4">
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>320</v>
+        <v>371</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>331</v>
+        <v>385</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>409</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>315</v>
+        <v>364</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>332</v>
+        <v>386</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="B7" s="4">
         <v>30000</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="B8" s="3">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>334</v>
+        <v>388</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="B9" s="4">
         <v>0.8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>335</v>
+        <v>389</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>337</v>
+        <v>391</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>317</v>
+        <v>280</v>
+      </c>
+      <c r="B12" s="3">
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>338</v>
+        <v>392</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="B13" s="4">
-        <v>1.4</v>
+        <v>20</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>339</v>
+        <v>393</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>318</v>
+        <v>282</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B15" s="4">
-        <v>1</v>
+        <v>283</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>366</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>128</v>
+        <v>375</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>341</v>
+        <v>395</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B16" s="3">
-        <v>80</v>
+        <v>284</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>367</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>324</v>
+        <v>375</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="B17" s="4">
-        <v>1500</v>
+        <v>1.4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>124</v>
+        <v>376</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B18" s="3">
-        <v>1500</v>
+        <v>286</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>368</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="B19" s="4">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="B20" s="3">
-        <v>14400</v>
+        <v>80</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>128</v>
+        <v>377</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>346</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="B21" s="4">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>325</v>
+        <v>143</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="B22" s="3">
-        <v>28800</v>
+        <v>1500</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="B23" s="4">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>320</v>
+        <v>147</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>349</v>
+        <v>403</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="B24" s="3">
-        <v>0.20997644</v>
+        <v>14400</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B25" s="4"/>
+        <v>293</v>
+      </c>
+      <c r="B25" s="4">
+        <v>28800</v>
+      </c>
       <c r="C25" s="4" t="s">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>351</v>
+        <v>405</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="B26" s="3">
-        <v>1913</v>
+        <v>20</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>326</v>
+        <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>352</v>
+        <v>406</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="B27" s="4">
-        <v>0.6114473499999999</v>
+        <v>0.5</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>353</v>
+        <v>407</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="B28" s="3">
-        <v>1913</v>
+        <v>45</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>354</v>
+        <v>408</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="B29" s="4">
-        <v>8245</v>
+        <v>30</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>326</v>
+        <v>143</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>355</v>
+        <v>409</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="B30" s="3">
-        <v>0.17857621</v>
+        <v>0.35</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>356</v>
+        <v>410</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="B31" s="4">
-        <v>8245</v>
+        <v>60</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>357</v>
+        <v>411</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B32" s="3"/>
+        <v>300</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>369</v>
+      </c>
       <c r="C32" s="3" t="s">
-        <v>326</v>
+        <v>140</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>358</v>
+        <v>412</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>410</v>
+        <v>477</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B33" s="4">
-        <v>0.55</v>
+        <v>301</v>
+      </c>
+      <c r="B33" s="4" t="b">
+        <v>1</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>327</v>
+        <v>156</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>359</v>
+        <v>413</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="B34" s="3">
-        <v>0.12</v>
+        <v>10</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>327</v>
+        <v>379</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>360</v>
+        <v>414</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="B35" s="4">
-        <v>0.03</v>
+        <v>28800</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>327</v>
+        <v>163</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>361</v>
+        <v>415</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="B36" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>362</v>
+        <v>416</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="B37" s="4">
-        <v>6</v>
+        <v>0.20997644</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>328</v>
+        <v>151</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>363</v>
+        <v>417</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B38" s="3">
-        <v>20</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>364</v>
+        <v>418</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B39" s="4"/>
+        <v>307</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1913</v>
+      </c>
       <c r="C39" s="4" t="s">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>365</v>
+        <v>419</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B40" s="3"/>
+        <v>308</v>
+      </c>
+      <c r="B40" s="3">
+        <v>0.6114473499999999</v>
+      </c>
       <c r="C40" s="3" t="s">
-        <v>328</v>
+        <v>151</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>366</v>
+        <v>420</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="B41" s="4">
-        <v>0.1</v>
+        <v>1913</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>367</v>
+        <v>421</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="B42" s="3">
-        <v>0.09</v>
+        <v>8245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="B43" s="4">
-        <v>0.08</v>
+        <v>0.17857621</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>327</v>
+        <v>151</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>369</v>
+        <v>423</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="B44" s="3">
-        <v>0.18</v>
+        <v>8245</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>370</v>
+        <v>424</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B45" s="4">
-        <v>0.14</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="B45" s="4"/>
       <c r="C45" s="4" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>371</v>
+        <v>425</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="B46" s="3">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>372</v>
+        <v>426</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="B47" s="4">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>373</v>
+        <v>427</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="B48" s="3">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>374</v>
+        <v>428</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="B49" s="4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>375</v>
+        <v>429</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="B50" s="3">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>376</v>
+        <v>430</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="B51" s="4">
-        <v>0.15</v>
+        <v>20</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>377</v>
+        <v>431</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B52" s="3">
-        <v>0.08</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B53" s="4">
-        <v>0.28</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="B53" s="4"/>
       <c r="C53" s="4" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>379</v>
+        <v>433</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="B54" s="3">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>380</v>
+        <v>434</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="B55" s="4">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="B56" s="3">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>382</v>
+        <v>436</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="B57" s="4">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>383</v>
+        <v>437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="B58" s="3">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>384</v>
+        <v>438</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
       <c r="B59" s="4">
         <v>0.1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="B60" s="3">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="B61" s="4">
-        <v>0.35</v>
+        <v>0.13</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>387</v>
+        <v>441</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="B62" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>388</v>
+        <v>442</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="B63" s="4">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>389</v>
+        <v>443</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="B64" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>390</v>
+        <v>444</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="34" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="B65" s="4">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>391</v>
+        <v>445</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="B66" s="3">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>392</v>
+        <v>446</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="34" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="B67" s="4">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>393</v>
+        <v>447</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="B68" s="3">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="34" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="B69" s="4">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>395</v>
+        <v>449</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="B70" s="3">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>396</v>
+        <v>450</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="34" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="B71" s="4">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>397</v>
+        <v>451</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>398</v>
+        <v>452</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="34" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="B73" s="4">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>399</v>
+        <v>453</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="34" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="B74" s="3">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>400</v>
+        <v>454</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="34" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
       <c r="B75" s="4">
         <v>0.15</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>401</v>
+        <v>455</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="34" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="B76" s="3">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>402</v>
+        <v>456</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="34" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="B77" s="4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="34" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="B78" s="3">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>404</v>
+        <v>458</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="34" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="B79" s="4">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>405</v>
+        <v>459</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="34" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="B80" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>406</v>
+        <v>460</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="34" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
       <c r="B81" s="4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>407</v>
+        <v>461</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>411</v>
+        <v>478</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="34" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="B82" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="34" customHeight="1">
+      <c r="A83" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B83" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="34" customHeight="1">
+      <c r="A84" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="34" customHeight="1">
+      <c r="A85" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B85" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="34" customHeight="1">
+      <c r="A86" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B86" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="34" customHeight="1">
+      <c r="A87" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B87" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="34" customHeight="1">
+      <c r="A88" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="34" customHeight="1">
+      <c r="A89" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B89" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="34" customHeight="1">
+      <c r="A90" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B90" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="34" customHeight="1">
+      <c r="A91" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B91" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="34" customHeight="1">
+      <c r="A92" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B92" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="34" customHeight="1">
+      <c r="A93" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B93" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="34" customHeight="1">
+      <c r="A94" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B94" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="34" customHeight="1">
+      <c r="A95" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B95" s="4">
         <v>0.7</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>411</v>
+      <c r="C95" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E82"/>
+  <autoFilter ref="A3:E95"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -5562,7 +6390,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -5572,7 +6400,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>501</v>
+        <v>592</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5582,7 +6410,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>413</v>
+        <v>480</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -5590,347 +6418,435 @@
     </row>
     <row r="4" spans="1:3" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>414</v>
+        <v>481</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>445</v>
+        <v>520</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>470</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>415</v>
+        <v>482</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>446</v>
+        <v>521</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>471</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>416</v>
+        <v>483</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>447</v>
+        <v>522</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>472</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>417</v>
+        <v>484</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>448</v>
+        <v>523</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>473</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>418</v>
+        <v>485</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>449</v>
+        <v>524</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>474</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>419</v>
+        <v>486</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>475</v>
+        <v>558</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>420</v>
+        <v>487</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>450</v>
+        <v>525</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>476</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>421</v>
+        <v>488</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>451</v>
+        <v>526</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>477</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>422</v>
+        <v>489</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>452</v>
+        <v>527</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>478</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>423</v>
+        <v>490</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>453</v>
+        <v>528</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>479</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>424</v>
+        <v>491</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>453</v>
+        <v>528</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>480</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>425</v>
+        <v>492</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>453</v>
+        <v>528</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>481</v>
+        <v>564</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>426</v>
+        <v>493</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>454</v>
+        <v>529</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>482</v>
+        <v>565</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>427</v>
+        <v>494</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>455</v>
+        <v>530</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>483</v>
+        <v>566</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>428</v>
+        <v>495</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>456</v>
+        <v>531</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>484</v>
+        <v>567</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>429</v>
+        <v>496</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>457</v>
+        <v>532</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>485</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>430</v>
+        <v>497</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>458</v>
+        <v>533</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>486</v>
+        <v>569</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>431</v>
+        <v>498</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>459</v>
+        <v>534</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>487</v>
+        <v>570</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>432</v>
+        <v>499</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>460</v>
+        <v>535</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>488</v>
+        <v>571</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>433</v>
+        <v>500</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>459</v>
+        <v>534</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>489</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>434</v>
+        <v>501</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>461</v>
+        <v>536</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>490</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>435</v>
+        <v>502</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>462</v>
+        <v>537</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>491</v>
+        <v>574</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>463</v>
+        <v>538</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>492</v>
+        <v>575</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>437</v>
+        <v>504</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>464</v>
+        <v>539</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>493</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>438</v>
+        <v>505</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>465</v>
+        <v>540</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>494</v>
+        <v>577</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>439</v>
+        <v>506</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>466</v>
+        <v>541</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>495</v>
+        <v>578</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>440</v>
+        <v>507</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>467</v>
+        <v>542</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>496</v>
+        <v>579</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>441</v>
+        <v>508</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>466</v>
+        <v>541</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>497</v>
+        <v>580</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>442</v>
+        <v>509</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>468</v>
+        <v>543</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>498</v>
+        <v>581</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>443</v>
+        <v>510</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>466</v>
+        <v>541</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>499</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>444</v>
+        <v>511</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>500</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="34" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="34" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="34" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="34" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="34" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="34" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="34" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="34" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:C34"/>
+  <autoFilter ref="A3:C42"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -5940,7 +6856,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -5949,7 +6865,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>639</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -5963,158 +6879,190 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>502</v>
+        <v>593</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>521</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>503</v>
+        <v>594</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>522</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>595</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>523</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>505</v>
+        <v>596</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>524</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>506</v>
+        <v>597</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>525</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>507</v>
+        <v>598</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>526</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>508</v>
+        <v>599</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>527</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>509</v>
+        <v>600</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>528</v>
+        <v>623</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>510</v>
+        <v>601</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>529</v>
+        <v>624</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>511</v>
+        <v>602</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>530</v>
+        <v>625</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>512</v>
+        <v>603</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>531</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>513</v>
+        <v>604</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>532</v>
+        <v>627</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>514</v>
+        <v>605</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>533</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>515</v>
+        <v>606</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>534</v>
+        <v>629</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>516</v>
+        <v>607</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>535</v>
+        <v>630</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>517</v>
+        <v>608</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>536</v>
+        <v>631</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>518</v>
+        <v>609</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>537</v>
+        <v>632</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>519</v>
+        <v>610</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>538</v>
+        <v>633</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>520</v>
+        <v>611</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>539</v>
+        <v>634</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="34" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="34" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="34" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="34" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B22"/>
+  <autoFilter ref="A3:B26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -6124,7 +7072,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -6133,7 +7081,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>587</v>
+        <v>700</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -6147,190 +7095,246 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>541</v>
+        <v>640</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>564</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>542</v>
+        <v>641</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>565</v>
+        <v>671</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>543</v>
+        <v>642</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>566</v>
+        <v>672</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>544</v>
+        <v>643</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>567</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>545</v>
+        <v>644</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>568</v>
+        <v>674</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>546</v>
+        <v>645</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>569</v>
+        <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>547</v>
+        <v>646</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>570</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>548</v>
+        <v>647</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>571</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>549</v>
+        <v>648</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>572</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>550</v>
+        <v>649</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>573</v>
+        <v>679</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>551</v>
+        <v>650</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>574</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>552</v>
+        <v>651</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>575</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>553</v>
+        <v>652</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>576</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>554</v>
+        <v>653</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>577</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>555</v>
+        <v>654</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>578</v>
+        <v>684</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>556</v>
+        <v>655</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>579</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>557</v>
+        <v>656</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>580</v>
+        <v>686</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>558</v>
+        <v>657</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>581</v>
+        <v>687</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>559</v>
+        <v>658</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>582</v>
+        <v>688</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>560</v>
+        <v>659</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>583</v>
+        <v>689</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>561</v>
+        <v>660</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>584</v>
+        <v>690</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>562</v>
+        <v>661</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>585</v>
+        <v>691</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>563</v>
+        <v>662</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>586</v>
+        <v>692</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="34" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="34" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="34" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="34" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="34" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="34" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="34" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B26"/>
+  <autoFilter ref="A3:B33"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
@@ -6340,7 +7344,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -6353,7 +7357,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>797</v>
+        <v>934</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6367,42 +7371,42 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>588</v>
+        <v>701</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>589</v>
+        <v>702</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>590</v>
+        <v>703</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>591</v>
+        <v>704</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>592</v>
+        <v>705</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>593</v>
+        <v>706</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>657</v>
+        <v>778</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>721</v>
+        <v>850</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>731</v>
+        <v>860</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G4" s="3">
         <v>25498039</v>
@@ -6410,22 +7414,22 @@
     </row>
     <row r="5" spans="1:7" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>594</v>
+        <v>707</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>658</v>
+        <v>779</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>721</v>
+        <v>850</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>732</v>
+        <v>861</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G5" s="4">
         <v>54288508</v>
@@ -6433,22 +7437,22 @@
     </row>
     <row r="6" spans="1:7" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>595</v>
+        <v>708</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>659</v>
+        <v>780</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>721</v>
+        <v>850</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>733</v>
+        <v>862</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G6" s="3">
         <v>43443363</v>
@@ -6456,22 +7460,22 @@
     </row>
     <row r="7" spans="1:7" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>596</v>
+        <v>709</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>660</v>
+        <v>781</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>721</v>
+        <v>850</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>734</v>
+        <v>863</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G7" s="4">
         <v>25498039</v>
@@ -6479,22 +7483,22 @@
     </row>
     <row r="8" spans="1:7" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>597</v>
+        <v>710</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>661</v>
+        <v>782</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>722</v>
+        <v>851</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>735</v>
+        <v>864</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G8" s="3">
         <v>1671168</v>
@@ -6502,22 +7506,22 @@
     </row>
     <row r="9" spans="1:7" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>598</v>
+        <v>711</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>662</v>
+        <v>783</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>722</v>
+        <v>851</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>736</v>
+        <v>865</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G9" s="4">
         <v>1970176</v>
@@ -6525,22 +7529,22 @@
     </row>
     <row r="10" spans="1:7" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>599</v>
+        <v>712</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>663</v>
+        <v>784</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>723</v>
+        <v>852</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>737</v>
+        <v>866</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G10" s="3">
         <v>18419712</v>
@@ -6548,22 +7552,22 @@
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>600</v>
+        <v>713</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>664</v>
+        <v>785</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>723</v>
+        <v>852</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>738</v>
+        <v>867</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G11" s="4">
         <v>26136576</v>
@@ -6571,22 +7575,22 @@
     </row>
     <row r="12" spans="1:7" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>601</v>
+        <v>714</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>665</v>
+        <v>786</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>739</v>
+        <v>868</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G12" s="3">
         <v>7745077</v>
@@ -6594,22 +7598,22 @@
     </row>
     <row r="13" spans="1:7" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>602</v>
+        <v>715</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>666</v>
+        <v>787</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>740</v>
+        <v>869</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G13" s="4">
         <v>503</v>
@@ -6617,22 +7621,22 @@
     </row>
     <row r="14" spans="1:7" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>603</v>
+        <v>716</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>667</v>
+        <v>788</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>741</v>
+        <v>870</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G14" s="3">
         <v>5241</v>
@@ -6640,22 +7644,22 @@
     </row>
     <row r="15" spans="1:7" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>604</v>
+        <v>717</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>668</v>
+        <v>789</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>742</v>
+        <v>871</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G15" s="4">
         <v>16899</v>
@@ -6663,22 +7667,22 @@
     </row>
     <row r="16" spans="1:7" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>605</v>
+        <v>718</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>669</v>
+        <v>790</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>743</v>
+        <v>872</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G16" s="3">
         <v>279475</v>
@@ -6686,22 +7690,22 @@
     </row>
     <row r="17" spans="1:7" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>606</v>
+        <v>719</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>670</v>
+        <v>791</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>744</v>
+        <v>873</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G17" s="4">
         <v>9488487</v>
@@ -6709,22 +7713,22 @@
     </row>
     <row r="18" spans="1:7" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>607</v>
+        <v>720</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>671</v>
+        <v>792</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>745</v>
+        <v>874</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G18" s="3">
         <v>11068</v>
@@ -6732,22 +7736,22 @@
     </row>
     <row r="19" spans="1:7" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>608</v>
+        <v>721</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>672</v>
+        <v>793</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>746</v>
+        <v>875</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G19" s="4">
         <v>14503</v>
@@ -6755,22 +7759,22 @@
     </row>
     <row r="20" spans="1:7" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>609</v>
+        <v>722</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>673</v>
+        <v>794</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>747</v>
+        <v>876</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G20" s="3">
         <v>11601</v>
@@ -6778,22 +7782,22 @@
     </row>
     <row r="21" spans="1:7" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>610</v>
+        <v>723</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>674</v>
+        <v>795</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>748</v>
+        <v>877</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G21" s="4">
         <v>921600</v>
@@ -6801,22 +7805,22 @@
     </row>
     <row r="22" spans="1:7" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>611</v>
+        <v>724</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>675</v>
+        <v>796</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>749</v>
+        <v>878</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G22" s="3">
         <v>4329472</v>
@@ -6824,64 +7828,64 @@
     </row>
     <row r="23" spans="1:7" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>612</v>
+        <v>725</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>676</v>
+        <v>797</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>750</v>
+        <v>879</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>613</v>
+        <v>726</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>677</v>
+        <v>798</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>751</v>
+        <v>880</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>614</v>
+        <v>727</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>678</v>
+        <v>799</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>752</v>
+        <v>881</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G25" s="4">
         <v>5040</v>
@@ -6889,22 +7893,22 @@
     </row>
     <row r="26" spans="1:7" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>615</v>
+        <v>728</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>679</v>
+        <v>800</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>753</v>
+        <v>882</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G26" s="3">
         <v>1213</v>
@@ -6912,22 +7916,22 @@
     </row>
     <row r="27" spans="1:7" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>616</v>
+        <v>729</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>680</v>
+        <v>801</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>724</v>
+        <v>853</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>754</v>
+        <v>883</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G27" s="4">
         <v>932</v>
@@ -6935,22 +7939,22 @@
     </row>
     <row r="28" spans="1:7" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>617</v>
+        <v>730</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>681</v>
+        <v>802</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>755</v>
+        <v>884</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G28" s="3">
         <v>1069056</v>
@@ -6958,22 +7962,22 @@
     </row>
     <row r="29" spans="1:7" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>618</v>
+        <v>731</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>682</v>
+        <v>803</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>756</v>
+        <v>885</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G29" s="4">
         <v>187087</v>
@@ -6981,22 +7985,22 @@
     </row>
     <row r="30" spans="1:7" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>619</v>
+        <v>732</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>683</v>
+        <v>804</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>757</v>
+        <v>886</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G30" s="3">
         <v>49996766</v>
@@ -7004,22 +8008,22 @@
     </row>
     <row r="31" spans="1:7" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>620</v>
+        <v>733</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>684</v>
+        <v>805</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>758</v>
+        <v>887</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G31" s="4">
         <v>47656187</v>
@@ -7027,22 +8031,22 @@
     </row>
     <row r="32" spans="1:7" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>621</v>
+        <v>734</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>685</v>
+        <v>806</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>759</v>
+        <v>888</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G32" s="3">
         <v>7427833</v>
@@ -7050,22 +8054,22 @@
     </row>
     <row r="33" spans="1:7" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>622</v>
+        <v>735</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>686</v>
+        <v>807</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>760</v>
+        <v>889</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G33" s="4">
         <v>226715</v>
@@ -7073,22 +8077,22 @@
     </row>
     <row r="34" spans="1:7" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>623</v>
+        <v>736</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>687</v>
+        <v>808</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>761</v>
+        <v>890</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G34" s="3">
         <v>3123</v>
@@ -7096,22 +8100,22 @@
     </row>
     <row r="35" spans="1:7" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>624</v>
+        <v>737</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>688</v>
+        <v>809</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>725</v>
+        <v>854</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>762</v>
+        <v>891</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G35" s="4">
         <v>1162</v>
@@ -7119,298 +8123,298 @@
     </row>
     <row r="36" spans="1:7" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>625</v>
+        <v>738</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>689</v>
+        <v>810</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>726</v>
+        <v>855</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>763</v>
+        <v>892</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G36" s="3">
-        <v>227102</v>
+        <v>223269</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>626</v>
+        <v>739</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>690</v>
+        <v>811</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>726</v>
+        <v>855</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>764</v>
+        <v>893</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G37" s="4">
-        <v>224907</v>
+        <v>213318</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>627</v>
+        <v>740</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>691</v>
+        <v>812</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>726</v>
+        <v>855</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>765</v>
+        <v>894</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G38" s="3">
-        <v>451839</v>
+        <v>435794</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>628</v>
+        <v>741</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>692</v>
+        <v>813</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>727</v>
+        <v>856</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>766</v>
+        <v>895</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G39" s="4">
-        <v>1288420</v>
+        <v>814048</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>629</v>
+        <v>742</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>693</v>
+        <v>814</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>727</v>
+        <v>856</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>767</v>
+        <v>896</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G40" s="3">
-        <v>1314652</v>
+        <v>816589</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>630</v>
+        <v>743</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>694</v>
+        <v>815</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>727</v>
+        <v>856</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>768</v>
+        <v>897</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G41" s="4">
-        <v>2602915</v>
+        <v>1630308</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>631</v>
+        <v>744</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>695</v>
+        <v>816</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>769</v>
+        <v>898</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G42" s="3">
-        <v>2109747</v>
+        <v>1584576</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>632</v>
+        <v>745</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>696</v>
+        <v>817</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>770</v>
+        <v>899</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G43" s="4">
-        <v>2106524</v>
+        <v>1544916</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>633</v>
+        <v>746</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>697</v>
+        <v>818</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>771</v>
+        <v>900</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G44" s="3">
-        <v>4216067</v>
+        <v>3129025</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>634</v>
+        <v>747</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>698</v>
+        <v>819</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>772</v>
+        <v>901</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G45" s="4">
-        <v>15617568</v>
+        <v>24490252</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>635</v>
+        <v>748</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>699</v>
+        <v>820</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>773</v>
+        <v>902</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G46" s="3">
-        <v>556</v>
+        <v>741</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>636</v>
+        <v>749</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>700</v>
+        <v>821</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>774</v>
+        <v>903</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G47" s="4">
-        <v>525</v>
+        <v>659</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>637</v>
+        <v>750</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>701</v>
+        <v>822</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>775</v>
+        <v>904</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G48" s="3">
         <v>17707008</v>
@@ -7418,367 +8422,367 @@
     </row>
     <row r="49" spans="1:7" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>638</v>
+        <v>751</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>702</v>
+        <v>823</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>776</v>
+        <v>905</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G49" s="4">
-        <v>714918</v>
+        <v>490620</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>639</v>
+        <v>752</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>703</v>
+        <v>824</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>777</v>
+        <v>906</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G50" s="3">
-        <v>745255</v>
+        <v>502297</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>640</v>
+        <v>753</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>704</v>
+        <v>825</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>778</v>
+        <v>907</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G51" s="4">
-        <v>1459825</v>
+        <v>992554</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>641</v>
+        <v>754</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>705</v>
+        <v>826</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>779</v>
+        <v>908</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G52" s="3">
-        <v>20062208</v>
+        <v>20082688</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>642</v>
+        <v>755</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>706</v>
+        <v>827</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>780</v>
+        <v>909</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G53" s="4">
-        <v>20447232</v>
+        <v>20459520</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>643</v>
+        <v>756</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>707</v>
+        <v>828</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>728</v>
+        <v>857</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>781</v>
+        <v>910</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G54" s="3">
-        <v>2492663</v>
+        <v>1725265</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>644</v>
+        <v>757</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>708</v>
+        <v>829</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>728</v>
+        <v>857</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>782</v>
+        <v>911</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G55" s="4">
-        <v>704</v>
+        <v>620</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>645</v>
+        <v>758</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>709</v>
+        <v>830</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>728</v>
+        <v>857</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>783</v>
+        <v>912</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G56" s="3">
-        <v>23400448</v>
+        <v>23285760</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>646</v>
+        <v>759</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>710</v>
+        <v>831</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>784</v>
+        <v>913</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G57" s="4">
-        <v>1094788</v>
+        <v>1013075</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>647</v>
+        <v>760</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>711</v>
+        <v>832</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>785</v>
+        <v>914</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G58" s="3">
-        <v>870164</v>
+        <v>817454</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>648</v>
+        <v>761</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>712</v>
+        <v>833</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>786</v>
+        <v>915</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G59" s="4">
-        <v>1095579</v>
+        <v>1021573</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>649</v>
+        <v>762</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>713</v>
+        <v>834</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>787</v>
+        <v>916</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G60" s="3">
-        <v>877549</v>
+        <v>826169</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>650</v>
+        <v>763</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>714</v>
+        <v>835</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>788</v>
+        <v>917</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G61" s="4">
-        <v>940952</v>
+        <v>874744</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>651</v>
+        <v>764</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>715</v>
+        <v>836</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>789</v>
+        <v>918</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G62" s="3">
-        <v>854357</v>
+        <v>793852</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>652</v>
+        <v>765</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>716</v>
+        <v>837</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>729</v>
+        <v>858</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>790</v>
+        <v>919</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G63" s="4">
-        <v>542</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>653</v>
+        <v>766</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>717</v>
+        <v>838</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>791</v>
+        <v>920</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G64" s="3">
         <v>23749</v>
@@ -7786,22 +8790,22 @@
     </row>
     <row r="65" spans="1:7" ht="34" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>654</v>
+        <v>767</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>718</v>
+        <v>839</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>792</v>
+        <v>921</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G65" s="4">
         <v>6348715</v>
@@ -7809,52 +8813,236 @@
     </row>
     <row r="66" spans="1:7" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>655</v>
+        <v>768</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>719</v>
+        <v>840</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>730</v>
+        <v>138</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>793</v>
+        <v>922</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G66" s="3">
-        <v>28579</v>
+        <v>779051</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="34" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>656</v>
+        <v>769</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>720</v>
+        <v>841</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>730</v>
+        <v>138</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>794</v>
+        <v>923</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>795</v>
+        <v>932</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>796</v>
+        <v>933</v>
       </c>
       <c r="G67" s="4">
+        <v>106524</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="34" customHeight="1">
+      <c r="A68" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="G68" s="3">
+        <v>108069</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="34" customHeight="1">
+      <c r="A69" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="G69" s="4">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="34" customHeight="1">
+      <c r="A70" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="34" customHeight="1">
+      <c r="A71" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="G71" s="4">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="34" customHeight="1">
+      <c r="A72" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="G72" s="3">
+        <v>13621</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="34" customHeight="1">
+      <c r="A73" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="G73" s="4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="34" customHeight="1">
+      <c r="A74" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="G74" s="3">
+        <v>28580</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="34" customHeight="1">
+      <c r="A75" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="G75" s="4">
         <v>80203</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G67"/>
+  <autoFilter ref="A3:G75"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/outputs/metadados_piloto.xlsx
+++ b/outputs/metadados_piloto.xlsx
@@ -16,11 +16,11 @@
     <sheet name="Arquivos gerados" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Arquivos gerados'!$A$3:$G$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Estatísticas!$A$3:$B$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Métodos de análise'!$A$3:$C$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Métodos de limpeza'!$A$3:$B$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Parâmetros!$A$3:$E$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resumo!$A$3:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variáveis!$A$3:$D$103</definedName>
   </definedNames>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="948">
   <si>
     <t>campo</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Piloto computacional de mobilidade urbana, diferenciação socioespacial e entropia socioeconômica de trajetórias</t>
   </si>
   <si>
-    <t>2026-09-28T12:46:33.726833+00:00</t>
+    <t>2026-09-28T13:51:19.688133+00:00</t>
   </si>
   <si>
     <t>português</t>
@@ -148,6 +148,12 @@
     <t>modal_edge_id</t>
   </si>
   <si>
+    <t>transit_physical_edge_id</t>
+  </si>
+  <si>
+    <t>spatial_geometry_valid</t>
+  </si>
+  <si>
     <t>mapping_mode</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
     <t>analysis_exclusion_reason</t>
   </si>
   <si>
-    <t>direct_spatial_mapping_failure</t>
-  </si>
-  <si>
-    <t>analysis_excluded_spatial_mapping</t>
-  </si>
-  <si>
     <t>sufficient_flow_both</t>
   </si>
   <si>
@@ -403,6 +403,9 @@
     <t>rede</t>
   </si>
   <si>
+    <t>rede física de transporte coletivo</t>
+  </si>
+  <si>
     <t>harmonização</t>
   </si>
   <si>
@@ -427,9 +430,6 @@
     <t>controle analítico</t>
   </si>
   <si>
-    <t>controle de espacialização transit</t>
-  </si>
-  <si>
     <t>GTFS</t>
   </si>
   <si>
@@ -478,6 +478,9 @@
     <t>identificador de aresta paralela</t>
   </si>
   <si>
+    <t>booleano</t>
+  </si>
+  <si>
     <t>identificador OSM</t>
   </si>
   <si>
@@ -499,9 +502,6 @@
     <t>índice normalizado de 0 a 1</t>
   </si>
   <si>
-    <t>booleano</t>
-  </si>
-  <si>
     <t>diferença de índice</t>
   </si>
   <si>
@@ -598,6 +598,12 @@
     <t>Identificador estável de uma aresta dentro de uma rede modal ou de uma conexão GTFS usada na trajetória</t>
   </si>
   <si>
+    <t>Identificador estável de um trecho físico GTFS compartilhado por conexões temporais equivalentes</t>
+  </si>
+  <si>
+    <t>Indica se a conexão temporal possui trecho físico GTFS com geometria válida para roteamento e análise espacial</t>
+  </si>
+  <si>
     <t>Rede ou fonte geométrica usada para associar a passagem ao analysis_segment_id sem alterar o modo principal da viagem</t>
   </si>
   <si>
@@ -694,13 +700,7 @@
     <t>Indica se o agente permanece na análise de trajetórias e H_soc após o controle pareado de outliers</t>
   </si>
   <si>
-    <t>Registra os motivos cumulativos pelos quais o agente é retirado da análise de trajetórias, incluindo outlier e falha de espacialização transit</t>
-  </si>
-  <si>
-    <t>Indica que o agente usa ao menos uma conexão GTFS sem correspondência válida na camada física comum</t>
-  </si>
-  <si>
-    <t>Indica que o agente foi retirado da análise espacial por falha direta de espacialização ou para preservar a exclusão pareada entre cenários</t>
+    <t>Registra o motivo pelo qual o agente é retirado da análise de trajetórias, atualmente associado ao controle pareado de outliers transit</t>
   </si>
   <si>
     <t>Indica se o fluxo mínimo para interpretação é atingido nos dois cenários</t>
@@ -934,9 +934,6 @@
     <t>transit.spatial_mapping.unmatched_policy</t>
   </si>
   <si>
-    <t>transit.spatial_mapping.paired_exclusion</t>
-  </si>
-  <si>
     <t>transit.routing.diagnostics.sample_size</t>
   </si>
   <si>
@@ -1138,7 +1135,7 @@
     <t>max_scheduled_trips</t>
   </si>
   <si>
-    <t>exclude_agent_paired</t>
+    <t>exclusive_segment</t>
   </si>
   <si>
     <t>agentes</t>
@@ -1267,10 +1264,7 @@
     <t>Diferença angular local máxima permitida na etapa de fallback</t>
   </si>
   <si>
-    <t>Política aplicada quando conexões GTFS usadas não encontram correspondência na camada física comum</t>
-  </si>
-  <si>
-    <t>Indica se a falha espacial de um agente em um cenário também retira o mesmo agent_id da análise espacial no outro cenário</t>
+    <t>Política aplicada quando um trecho físico GTFS válido não encontra correspondência segura nas redes OSM e precisa ser incorporado à camada comum</t>
   </si>
   <si>
     <t>Quantidade de pares origem-destino usada no diagnóstico técnico do roteador temporal</t>
@@ -1576,21 +1570,24 @@
     <t>Extração parcial do shape GTFS</t>
   </si>
   <si>
+    <t>Construção da rede física GTFS completa</t>
+  </si>
+  <si>
     <t>Mapeamento geométrico de transit para segmentos físicos</t>
   </si>
   <si>
     <t>Mapeamento espacial hierárquico do transporte coletivo</t>
   </si>
   <si>
+    <t>Integração da rede física GTFS à camada comum</t>
+  </si>
+  <si>
     <t>Recuperação ordenada da posição de paradas no shape</t>
   </si>
   <si>
     <t>Filtro pareado de outliers de trajetórias transit</t>
   </si>
   <si>
-    <t>Exclusão pareada por falha de espacialização transit</t>
-  </si>
-  <si>
     <t>generate_population</t>
   </si>
   <si>
@@ -1675,21 +1672,24 @@
     <t>build_used_transit_connection_geometries</t>
   </si>
   <si>
+    <t>build_transit_physical_network</t>
+  </si>
+  <si>
     <t>map_transit_connections_to_analysis_segments</t>
   </si>
   <si>
     <t>map_transit_connections_hierarchically</t>
   </si>
   <si>
+    <t>integrate_transit_physical_network</t>
+  </si>
+  <si>
     <t>_forward_stop_positions</t>
   </si>
   <si>
     <t>apply_paired_transit_outlier_filter</t>
   </si>
   <si>
-    <t>apply_paired_transit_spatial_exclusions</t>
-  </si>
-  <si>
     <t>Gera agentes sintéticos preservando as participações configuradas para os grupos de renda</t>
   </si>
   <si>
@@ -1789,13 +1789,19 @@
     <t>Decompõe uma viagem transit em caminhada de acesso, conexões embarcadas e caminhada de egresso preservando transit como modo principal da viagem</t>
   </si>
   <si>
-    <t>Recorta a geometria do shape somente entre as posições das paradas consecutivas efetivamente usadas pelas conexões selecionadas</t>
+    <t>Recorta a geometria do shape entre posições consecutivas de parada e também é reutilizado na construção da rede física GTFS completa</t>
+  </si>
+  <si>
+    <t>Agrupa conexões temporais repetidas em trechos físicos estáveis independentes de horário, viagem, cenário, seed e tamanho da população sintética</t>
   </si>
   <si>
     <t>Associa trechos GTFS usados aos segmentos físicos usando proximidade, cobertura do segmento ou do shape e compatibilidade da orientação local</t>
   </si>
   <si>
-    <t>Procura primeiro correspondência em segmentos com suporte da rede car e aplica uma segunda etapa na rede física completa somente às conexões ainda não mapeadas</t>
+    <t>Procura primeiro correspondência em segmentos com suporte da rede car e aplica uma segunda etapa na rede física completa aos trechos GTFS ainda não associados</t>
+  </si>
+  <si>
+    <t>Integra todos os trechos físicos GTFS válidos à camada comum e cria analysis_segment_id exclusivos para trechos que não possuem correspondência segura nas redes OSM</t>
   </si>
   <si>
     <t>Seleciona projeções sucessivas das paradas ao longo do shape quando as posições processadas estão ausentes, iguais ou decrescentes, preservando a ordem do deslocamento</t>
@@ -1804,9 +1810,6 @@
     <t>Calcula limites robustos com os dois cenários combinados, identifica distância extrema ou circuity extrema acompanhada de rota longa e propaga a exclusão ao mesmo agent_id nos dois cenários</t>
   </si>
   <si>
-    <t>Identifica agentes cujas conexões GTFS usadas não possuem correspondência na camada física comum e retira o mesmo agent_id da análise espacial nos dois cenários quando o pareamento está habilitado</t>
-  </si>
-  <si>
     <t>Metadados do piloto — Métodos de análise</t>
   </si>
   <si>
@@ -1870,7 +1873,7 @@
     <t>Cobertura geométrica do shape</t>
   </si>
   <si>
-    <t>Taxa de sucesso do mapeamento espacial transit</t>
+    <t>Cobertura da rede física transit</t>
   </si>
   <si>
     <t>Cerca externa superior de Tukey</t>
@@ -1939,7 +1942,7 @@
     <t>Mede o percentual do trecho GTFS usado que fica coberto pelos segmentos físicos associados dentro da tolerância espacial</t>
   </si>
   <si>
-    <t>Calcula a proporção das conexões GTFS usadas que possuem geometria válida e correspondência com pelo menos um analysis_segment_id</t>
+    <t>Quantifica trechos físicos GTFS associados na etapa primária, na etapa de fallback e incorporados como segmentos exclusivos transit</t>
   </si>
   <si>
     <t>Calcula Q3 mais três vezes o intervalo interquartil por padrão para identificar valores extremos sem depender da média ou do desvio padrão</t>
@@ -2038,7 +2041,7 @@
     <t>Critério conservador de distância e circuity</t>
   </si>
   <si>
-    <t>Exclusão pareada de falhas de espacialização transit</t>
+    <t>Incorporação de trechos transit exclusivos</t>
   </si>
   <si>
     <t>Remove espaços excedentes e normaliza campos textuais usados como identificadores e categorias</t>
@@ -2128,7 +2131,7 @@
     <t>Exclui distância roteada acima da cerca externa ou circuity acima da cerca externa quando a rota também está acima do terceiro quartil, evitando excluir viagens curtas apenas por apresentarem razão elevada</t>
   </si>
   <si>
-    <t>Retira da análise de H_soc toda a trajetória do agente quando ao menos uma conexão GTFS usada não pode ser associada a analysis_segment_id e aplica a mesma retirada ao agent_id correspondente no outro cenário</t>
+    <t>Preserva a trajetória do agente ao criar um analysis_segment_id exclusivo para trechos físicos GTFS válidos que não possuem correspondência segura nas redes OSM</t>
   </si>
   <si>
     <t>Metadados do piloto — Métodos de limpeza</t>
@@ -2233,6 +2236,18 @@
     <t>transit_connections_routable_processed.parquet</t>
   </si>
   <si>
+    <t>transit_connections_spatial_routable_processed.parquet</t>
+  </si>
+  <si>
+    <t>transit_physical_edges_processed.gpkg</t>
+  </si>
+  <si>
+    <t>transit_physical_edge_diagnostics_processed.csv</t>
+  </si>
+  <si>
+    <t>transit_connection_to_physical_edge_processed.parquet</t>
+  </si>
+  <si>
     <t>transit_trip_quality_processed.csv</t>
   </si>
   <si>
@@ -2254,6 +2269,15 @@
     <t>agents_all_scenarios.csv</t>
   </si>
   <si>
+    <t>edge_usage_routed_baseline.csv</t>
+  </si>
+  <si>
+    <t>edge_usage_routed_differentiated.csv</t>
+  </si>
+  <si>
+    <t>edge_usage_routed_all_scenarios.csv</t>
+  </si>
+  <si>
     <t>edge_usage_baseline.csv</t>
   </si>
   <si>
@@ -2335,16 +2359,13 @@
     <t>gtfs_trip_temporal_quality.csv</t>
   </si>
   <si>
-    <t>transit_connection_to_analysis_segment.csv</t>
-  </si>
-  <si>
-    <t>transit_connection_geometry_diagnostics.csv</t>
-  </si>
-  <si>
-    <t>transit_connection_match_diagnostics.csv</t>
-  </si>
-  <si>
-    <t>transit_spatial_match_report.csv</t>
+    <t>transit_physical_edge_to_analysis_segment.csv</t>
+  </si>
+  <si>
+    <t>transit_physical_match_diagnostics.csv</t>
+  </si>
+  <si>
+    <t>transit_physical_network_summary.csv</t>
   </si>
   <si>
     <t>outlier_exclusions.csv</t>
@@ -2353,12 +2374,6 @@
     <t>outlier_filter_summary.csv</t>
   </si>
   <si>
-    <t>transit_spatial_exclusions.csv</t>
-  </si>
-  <si>
-    <t>transit_spatial_exclusion_summary.csv</t>
-  </si>
-  <si>
     <t>metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -2449,6 +2464,18 @@
     <t>data/gtfs/transit_connections_routable_processed.parquet</t>
   </si>
   <si>
+    <t>data/gtfs/transit_connections_spatial_routable_processed.parquet</t>
+  </si>
+  <si>
+    <t>data/gtfs/transit_physical_edges_processed.gpkg</t>
+  </si>
+  <si>
+    <t>data/gtfs/transit_physical_edge_diagnostics_processed.csv</t>
+  </si>
+  <si>
+    <t>data/gtfs/transit_connection_to_physical_edge_processed.parquet</t>
+  </si>
+  <si>
     <t>data/gtfs/transit_trip_quality_processed.csv</t>
   </si>
   <si>
@@ -2470,6 +2497,15 @@
     <t>outputs/pilot/agents_all_scenarios.csv</t>
   </si>
   <si>
+    <t>outputs/pilot/edge_usage_routed_baseline.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/edge_usage_routed_differentiated.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/edge_usage_routed_all_scenarios.csv</t>
+  </si>
+  <si>
     <t>outputs/pilot/edge_usage_baseline.csv</t>
   </si>
   <si>
@@ -2551,16 +2587,13 @@
     <t>outputs/pilot/gtfs_trip_temporal_quality.csv</t>
   </si>
   <si>
-    <t>outputs/pilot/transit_connection_to_analysis_segment.csv</t>
-  </si>
-  <si>
-    <t>outputs/pilot/transit_connection_geometry_diagnostics.csv</t>
-  </si>
-  <si>
-    <t>outputs/pilot/transit_connection_match_diagnostics.csv</t>
-  </si>
-  <si>
-    <t>outputs/pilot/transit_spatial_match_report.csv</t>
+    <t>outputs/pilot/transit_physical_edge_to_analysis_segment.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/transit_physical_match_diagnostics.csv</t>
+  </si>
+  <si>
+    <t>outputs/pilot/transit_physical_network_summary.csv</t>
   </si>
   <si>
     <t>outputs/pilot/outlier_exclusions.csv</t>
@@ -2569,12 +2602,6 @@
     <t>outputs/pilot/outlier_filter_summary.csv</t>
   </si>
   <si>
-    <t>outputs/pilot/transit_spatial_exclusions.csv</t>
-  </si>
-  <si>
-    <t>outputs/pilot/transit_spatial_exclusion_summary.csv</t>
-  </si>
-  <si>
     <t>outputs/metadados_piloto.xlsx</t>
   </si>
   <si>
@@ -2695,6 +2722,18 @@
     <t>Subconjunto das conexões GTFS cujas viagens atendem aos critérios técnicos de qualidade temporal usados pelo roteador</t>
   </si>
   <si>
+    <t>Subconjunto das conexões temporalmente válidas que também possuem representação física GTFS válida e é usado pelo roteador integrado</t>
+  </si>
+  <si>
+    <t>Rede física completa de trechos GTFS stop a stop com identificadores estáveis independentes de cenário e população sintética</t>
+  </si>
+  <si>
+    <t>Diagnóstico da extração geométrica de cada trecho físico GTFS, incluindo método de posição e distâncias de snap</t>
+  </si>
+  <si>
+    <t>Correspondência entre cada connection_id temporal e seu transit_physical_edge_id estável</t>
+  </si>
+  <si>
     <t>Diagnóstico por trip_id com critérios e motivos de inclusão ou exclusão da tabela de conexões roteáveis</t>
   </si>
   <si>
@@ -2716,13 +2755,22 @@
     <t>Agentes dos dois cenários reunidos em uma única tabela</t>
   </si>
   <si>
-    <t>Registros agente × aresta modal do cenário baseline</t>
-  </si>
-  <si>
-    <t>Registros agente × aresta modal do cenário differentiated</t>
-  </si>
-  <si>
-    <t>Registros agente × aresta modal dos dois cenários</t>
+    <t>Registros agente × aresta modal do baseline antes da exclusão de outliers, preservados para auditoria</t>
+  </si>
+  <si>
+    <t>Registros agente × aresta modal do differentiated antes da exclusão de outliers, preservados para auditoria</t>
+  </si>
+  <si>
+    <t>Registros agente × aresta modal dos dois cenários antes da exclusão de outliers</t>
+  </si>
+  <si>
+    <t>Registros agente × aresta modal do baseline após o filtro pareado de outliers e antes da harmonização espacial</t>
+  </si>
+  <si>
+    <t>Registros agente × aresta modal do differentiated após o filtro pareado de outliers e antes da harmonização espacial</t>
+  </si>
+  <si>
+    <t>Registros agente × aresta modal dos dois cenários após o filtro pareado de outliers</t>
   </si>
   <si>
     <t>Uso das arestas do baseline associado aos segmentos físicos comuns</t>
@@ -2743,7 +2791,7 @@
     <t>Resumo dos métodos e da qualidade de harmonização restrito às arestas usadas pelos agentes</t>
   </si>
   <si>
-    <t>Camada completa dos segmentos físicos usados como unidade comum de análise</t>
+    <t>Camada completa dos segmentos físicos usados como unidade comum de análise, incluindo segmentos transit exclusivos quando ausentes nas redes OSM</t>
   </si>
   <si>
     <t>Estatísticas de fluxo, composição socioeconômica e H_soc do cenário baseline</t>
@@ -2797,28 +2845,19 @@
     <t>Diagnóstico por trip_id com duração programada, pontos temporais originais, conexões de duração zero e velocidade implícita pelo shape</t>
   </si>
   <si>
-    <t>Mapeamento das conexões GTFS usadas pelos agentes para os segmentos físicos comuns do piloto</t>
-  </si>
-  <si>
-    <t>Diagnóstico da disponibilidade e validade da geometria parcial de cada conexão GTFS usada</t>
-  </si>
-  <si>
-    <t>Diagnóstico de quantidade de segmentos associados e cobertura geométrica por conexão GTFS usada</t>
-  </si>
-  <si>
-    <t>Resumo da cobertura e do sucesso do mapeamento espacial das conexões GTFS usadas</t>
+    <t>Mapeamento da rede física GTFS completa para analysis_segment_id existentes ou exclusivos transit</t>
+  </si>
+  <si>
+    <t>Diagnóstico da etapa primária, fallback ou incorporação exclusiva aplicada a cada trecho físico GTFS</t>
+  </si>
+  <si>
+    <t>Resumo quantitativo da integração da rede física GTFS completa à camada comum de análise</t>
   </si>
   <si>
     <t>Registro auditável de cada cenário e agente retirado da análise de trajetórias por outlier transit direto ou exclusão pareada</t>
   </si>
   <si>
     <t>Resumo do método, quartis, cercas externas e quantidade de outliers identificados no piloto</t>
-  </si>
-  <si>
-    <t>Registro por cenário e agente retirado da análise por conexões GTFS sem correspondência espacial, incluindo rotas e viagens afetadas</t>
-  </si>
-  <si>
-    <t>Resumo da quantidade de conexões sem correspondência e de agentes afetados pela exclusão espacial pareada</t>
   </si>
   <si>
     <t>Planilha consolidada com variáveis, parâmetros, métodos, estatísticas, limpeza e arquivos do piloto</t>
@@ -3307,7 +3346,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
@@ -3331,7 +3370,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -3650,7 +3689,7 @@
         <v>124</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>189</v>
@@ -3661,10 +3700,10 @@
         <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>190</v>
@@ -3689,10 +3728,10 @@
         <v>42</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>192</v>
@@ -3703,10 +3742,10 @@
         <v>43</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>193</v>
@@ -3720,7 +3759,7 @@
         <v>123</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>194</v>
@@ -3731,10 +3770,10 @@
         <v>45</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>195</v>
@@ -3745,10 +3784,10 @@
         <v>46</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>196</v>
@@ -3759,10 +3798,10 @@
         <v>47</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>197</v>
@@ -3773,10 +3812,10 @@
         <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>198</v>
@@ -3787,10 +3826,10 @@
         <v>49</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>199</v>
@@ -3801,7 +3840,7 @@
         <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>153</v>
@@ -3815,10 +3854,10 @@
         <v>51</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>201</v>
@@ -3829,10 +3868,10 @@
         <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>202</v>
@@ -3843,10 +3882,10 @@
         <v>53</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>203</v>
@@ -3857,10 +3896,10 @@
         <v>54</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>204</v>
@@ -3871,10 +3910,10 @@
         <v>55</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>205</v>
@@ -3885,10 +3924,10 @@
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>206</v>
@@ -3902,7 +3941,7 @@
         <v>127</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>207</v>
@@ -3916,7 +3955,7 @@
         <v>127</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>208</v>
@@ -3944,7 +3983,7 @@
         <v>128</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>210</v>
@@ -3955,10 +3994,10 @@
         <v>61</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>211</v>
@@ -3969,10 +4008,10 @@
         <v>62</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>212</v>
@@ -3986,7 +4025,7 @@
         <v>129</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>213</v>
@@ -4000,7 +4039,7 @@
         <v>129</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>214</v>
@@ -4011,10 +4050,10 @@
         <v>65</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>215</v>
@@ -4025,10 +4064,10 @@
         <v>66</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>216</v>
@@ -4039,10 +4078,10 @@
         <v>67</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>217</v>
@@ -4056,7 +4095,7 @@
         <v>130</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>218</v>
@@ -4070,7 +4109,7 @@
         <v>130</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>219</v>
@@ -4081,10 +4120,10 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>220</v>
@@ -4098,7 +4137,7 @@
         <v>131</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>221</v>
@@ -4109,10 +4148,10 @@
         <v>72</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>222</v>
@@ -4126,7 +4165,7 @@
         <v>132</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>223</v>
@@ -4137,10 +4176,10 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>224</v>
@@ -4294,7 +4333,7 @@
         <v>133</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>235</v>
@@ -4308,7 +4347,7 @@
         <v>133</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>236</v>
@@ -4322,7 +4361,7 @@
         <v>133</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>237</v>
@@ -4350,7 +4389,7 @@
         <v>133</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>239</v>
@@ -4378,7 +4417,7 @@
         <v>133</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>241</v>
@@ -4392,7 +4431,7 @@
         <v>134</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>242</v>
@@ -4658,7 +4697,7 @@
         <v>134</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>261</v>
@@ -4672,7 +4711,7 @@
         <v>134</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>262</v>
@@ -4787,7 +4826,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.7109375" customWidth="1"/>
@@ -4799,7 +4838,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4831,13 +4870,13 @@
         <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="34" customHeight="1">
@@ -4848,13 +4887,13 @@
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34" customHeight="1">
@@ -4862,16 +4901,16 @@
         <v>274</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34" customHeight="1">
@@ -4885,10 +4924,10 @@
         <v>143</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="34" customHeight="1">
@@ -4902,10 +4941,10 @@
         <v>143</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="34" customHeight="1">
@@ -4916,13 +4955,13 @@
         <v>0.8</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="34" customHeight="1">
@@ -4933,13 +4972,13 @@
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="34" customHeight="1">
@@ -4947,16 +4986,16 @@
         <v>279</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="34" customHeight="1">
@@ -4967,13 +5006,13 @@
         <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" customHeight="1">
@@ -4984,13 +5023,13 @@
         <v>20</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" customHeight="1">
@@ -5001,13 +5040,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="34" customHeight="1">
@@ -5015,16 +5054,16 @@
         <v>283</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34" customHeight="1">
@@ -5032,16 +5071,16 @@
         <v>284</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="34" customHeight="1">
@@ -5052,13 +5091,13 @@
         <v>1.4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="34" customHeight="1">
@@ -5066,16 +5105,16 @@
         <v>286</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="34" customHeight="1">
@@ -5089,10 +5128,10 @@
         <v>147</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="34" customHeight="1">
@@ -5103,13 +5142,13 @@
         <v>80</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="34" customHeight="1">
@@ -5123,10 +5162,10 @@
         <v>143</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="34" customHeight="1">
@@ -5140,10 +5179,10 @@
         <v>143</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="34" customHeight="1">
@@ -5157,10 +5196,10 @@
         <v>147</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="34" customHeight="1">
@@ -5174,10 +5213,10 @@
         <v>147</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="34" customHeight="1">
@@ -5191,10 +5230,10 @@
         <v>163</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="34" customHeight="1">
@@ -5208,10 +5247,10 @@
         <v>143</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="34" customHeight="1">
@@ -5222,13 +5261,13 @@
         <v>0.5</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="34" customHeight="1">
@@ -5239,13 +5278,13 @@
         <v>45</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="34" customHeight="1">
@@ -5259,10 +5298,10 @@
         <v>143</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="34" customHeight="1">
@@ -5273,13 +5312,13 @@
         <v>0.35</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="34" customHeight="1">
@@ -5290,13 +5329,13 @@
         <v>60</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1">
@@ -5304,33 +5343,33 @@
         <v>300</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>140</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B33" s="4" t="b">
-        <v>1</v>
+      <c r="B33" s="4">
+        <v>10</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>156</v>
+        <v>378</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="34" customHeight="1">
@@ -5338,16 +5377,16 @@
         <v>302</v>
       </c>
       <c r="B34" s="3">
-        <v>10</v>
+        <v>28800</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>379</v>
+        <v>163</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="34" customHeight="1">
@@ -5355,16 +5394,16 @@
         <v>303</v>
       </c>
       <c r="B35" s="4">
-        <v>28800</v>
+        <v>42</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>163</v>
+        <v>370</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="34" customHeight="1">
@@ -5372,48 +5411,48 @@
         <v>304</v>
       </c>
       <c r="B36" s="3">
-        <v>42</v>
+        <v>0.20997644</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>371</v>
+        <v>152</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="B37" s="4">
-        <v>0.20997644</v>
-      </c>
+      <c r="B37" s="4"/>
       <c r="C37" s="4" t="s">
-        <v>151</v>
+        <v>379</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B38" s="3"/>
+      <c r="B38" s="3">
+        <v>1913</v>
+      </c>
       <c r="C38" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="34" customHeight="1">
@@ -5421,16 +5460,16 @@
         <v>307</v>
       </c>
       <c r="B39" s="4">
-        <v>1913</v>
+        <v>0.6114473499999999</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>380</v>
+        <v>152</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="34" customHeight="1">
@@ -5438,16 +5477,16 @@
         <v>308</v>
       </c>
       <c r="B40" s="3">
-        <v>0.6114473499999999</v>
+        <v>1913</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>151</v>
+        <v>379</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="34" customHeight="1">
@@ -5455,16 +5494,16 @@
         <v>309</v>
       </c>
       <c r="B41" s="4">
-        <v>1913</v>
+        <v>8245</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="34" customHeight="1">
@@ -5472,16 +5511,16 @@
         <v>310</v>
       </c>
       <c r="B42" s="3">
-        <v>8245</v>
+        <v>0.17857621</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>380</v>
+        <v>152</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="34" customHeight="1">
@@ -5489,48 +5528,48 @@
         <v>311</v>
       </c>
       <c r="B43" s="4">
-        <v>0.17857621</v>
+        <v>8245</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>151</v>
+        <v>379</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B44" s="3">
-        <v>8245</v>
-      </c>
+      <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="B45" s="4"/>
+      <c r="B45" s="4">
+        <v>0.55</v>
+      </c>
       <c r="C45" s="4" t="s">
         <v>380</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="34" customHeight="1">
@@ -5538,16 +5577,16 @@
         <v>314</v>
       </c>
       <c r="B46" s="3">
-        <v>0.55</v>
+        <v>0.12</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="34" customHeight="1">
@@ -5555,16 +5594,16 @@
         <v>315</v>
       </c>
       <c r="B47" s="4">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="34" customHeight="1">
@@ -5572,16 +5611,16 @@
         <v>316</v>
       </c>
       <c r="B48" s="3">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="34" customHeight="1">
@@ -5589,16 +5628,16 @@
         <v>317</v>
       </c>
       <c r="B49" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>381</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="34" customHeight="1">
@@ -5606,33 +5645,31 @@
         <v>318</v>
       </c>
       <c r="B50" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B51" s="4">
-        <v>20</v>
-      </c>
+      <c r="B51" s="4"/>
       <c r="C51" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="34" customHeight="1">
@@ -5641,28 +5678,30 @@
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B53" s="4"/>
+      <c r="B53" s="4">
+        <v>0.1</v>
+      </c>
       <c r="C53" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="34" customHeight="1">
@@ -5670,16 +5709,16 @@
         <v>322</v>
       </c>
       <c r="B54" s="3">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="34" customHeight="1">
@@ -5687,16 +5726,16 @@
         <v>323</v>
       </c>
       <c r="B55" s="4">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="34" customHeight="1">
@@ -5704,16 +5743,16 @@
         <v>324</v>
       </c>
       <c r="B56" s="3">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="34" customHeight="1">
@@ -5721,16 +5760,16 @@
         <v>325</v>
       </c>
       <c r="B57" s="4">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="34" customHeight="1">
@@ -5738,16 +5777,16 @@
         <v>326</v>
       </c>
       <c r="B58" s="3">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="34" customHeight="1">
@@ -5755,16 +5794,16 @@
         <v>327</v>
       </c>
       <c r="B59" s="4">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="34" customHeight="1">
@@ -5772,16 +5811,16 @@
         <v>328</v>
       </c>
       <c r="B60" s="3">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="34" customHeight="1">
@@ -5789,16 +5828,16 @@
         <v>329</v>
       </c>
       <c r="B61" s="4">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="34" customHeight="1">
@@ -5806,16 +5845,16 @@
         <v>330</v>
       </c>
       <c r="B62" s="3">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="34" customHeight="1">
@@ -5823,16 +5862,16 @@
         <v>331</v>
       </c>
       <c r="B63" s="4">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="34" customHeight="1">
@@ -5840,16 +5879,16 @@
         <v>332</v>
       </c>
       <c r="B64" s="3">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="34" customHeight="1">
@@ -5857,16 +5896,16 @@
         <v>333</v>
       </c>
       <c r="B65" s="4">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="34" customHeight="1">
@@ -5874,16 +5913,16 @@
         <v>334</v>
       </c>
       <c r="B66" s="3">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="34" customHeight="1">
@@ -5891,16 +5930,16 @@
         <v>335</v>
       </c>
       <c r="B67" s="4">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="34" customHeight="1">
@@ -5908,16 +5947,16 @@
         <v>336</v>
       </c>
       <c r="B68" s="3">
-        <v>0.08</v>
+        <v>0.45</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="34" customHeight="1">
@@ -5925,16 +5964,16 @@
         <v>337</v>
       </c>
       <c r="B69" s="4">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="34" customHeight="1">
@@ -5942,16 +5981,16 @@
         <v>338</v>
       </c>
       <c r="B70" s="3">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="34" customHeight="1">
@@ -5959,16 +5998,16 @@
         <v>339</v>
       </c>
       <c r="B71" s="4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="34" customHeight="1">
@@ -5979,13 +6018,13 @@
         <v>0.1</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="34" customHeight="1">
@@ -5993,16 +6032,16 @@
         <v>341</v>
       </c>
       <c r="B73" s="4">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="34" customHeight="1">
@@ -6010,16 +6049,16 @@
         <v>342</v>
       </c>
       <c r="B74" s="3">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="34" customHeight="1">
@@ -6027,16 +6066,16 @@
         <v>343</v>
       </c>
       <c r="B75" s="4">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="34" customHeight="1">
@@ -6044,16 +6083,16 @@
         <v>344</v>
       </c>
       <c r="B76" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="34" customHeight="1">
@@ -6061,16 +6100,16 @@
         <v>345</v>
       </c>
       <c r="B77" s="4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="34" customHeight="1">
@@ -6078,16 +6117,16 @@
         <v>346</v>
       </c>
       <c r="B78" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="34" customHeight="1">
@@ -6095,16 +6134,16 @@
         <v>347</v>
       </c>
       <c r="B79" s="4">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="34" customHeight="1">
@@ -6112,16 +6151,16 @@
         <v>348</v>
       </c>
       <c r="B80" s="3">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="34" customHeight="1">
@@ -6129,16 +6168,16 @@
         <v>349</v>
       </c>
       <c r="B81" s="4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="34" customHeight="1">
@@ -6146,16 +6185,16 @@
         <v>350</v>
       </c>
       <c r="B82" s="3">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="34" customHeight="1">
@@ -6166,13 +6205,13 @@
         <v>0.25</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="34" customHeight="1">
@@ -6180,16 +6219,16 @@
         <v>352</v>
       </c>
       <c r="B84" s="3">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="34" customHeight="1">
@@ -6197,16 +6236,16 @@
         <v>353</v>
       </c>
       <c r="B85" s="4">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="34" customHeight="1">
@@ -6214,16 +6253,16 @@
         <v>354</v>
       </c>
       <c r="B86" s="3">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="34" customHeight="1">
@@ -6231,16 +6270,16 @@
         <v>355</v>
       </c>
       <c r="B87" s="4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="34" customHeight="1">
@@ -6251,13 +6290,13 @@
         <v>0.15</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="34" customHeight="1">
@@ -6265,16 +6304,16 @@
         <v>357</v>
       </c>
       <c r="B89" s="4">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="34" customHeight="1">
@@ -6282,16 +6321,16 @@
         <v>358</v>
       </c>
       <c r="B90" s="3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="34" customHeight="1">
@@ -6299,16 +6338,16 @@
         <v>359</v>
       </c>
       <c r="B91" s="4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="34" customHeight="1">
@@ -6319,13 +6358,13 @@
         <v>0.1</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="34" customHeight="1">
@@ -6336,13 +6375,13 @@
         <v>0.1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="34" customHeight="1">
@@ -6350,37 +6389,20 @@
         <v>362</v>
       </c>
       <c r="B94" s="3">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="34" customHeight="1">
-      <c r="A95" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B95" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E95"/>
+  <autoFilter ref="A3:E94"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -6390,7 +6412,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.7109375" customWidth="1"/>
@@ -6400,7 +6422,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6410,7 +6432,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -6418,10 +6440,10 @@
     </row>
     <row r="4" spans="1:3" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>553</v>
@@ -6429,10 +6451,10 @@
     </row>
     <row r="5" spans="1:3" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>554</v>
@@ -6440,10 +6462,10 @@
     </row>
     <row r="6" spans="1:3" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>555</v>
@@ -6451,10 +6473,10 @@
     </row>
     <row r="7" spans="1:3" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>556</v>
@@ -6462,10 +6484,10 @@
     </row>
     <row r="8" spans="1:3" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>557</v>
@@ -6473,10 +6495,10 @@
     </row>
     <row r="9" spans="1:3" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>558</v>
@@ -6484,10 +6506,10 @@
     </row>
     <row r="10" spans="1:3" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>559</v>
@@ -6495,10 +6517,10 @@
     </row>
     <row r="11" spans="1:3" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>560</v>
@@ -6506,10 +6528,10 @@
     </row>
     <row r="12" spans="1:3" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>561</v>
@@ -6517,10 +6539,10 @@
     </row>
     <row r="13" spans="1:3" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>562</v>
@@ -6528,10 +6550,10 @@
     </row>
     <row r="14" spans="1:3" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>563</v>
@@ -6539,10 +6561,10 @@
     </row>
     <row r="15" spans="1:3" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>564</v>
@@ -6550,10 +6572,10 @@
     </row>
     <row r="16" spans="1:3" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>565</v>
@@ -6561,10 +6583,10 @@
     </row>
     <row r="17" spans="1:3" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>566</v>
@@ -6572,10 +6594,10 @@
     </row>
     <row r="18" spans="1:3" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>567</v>
@@ -6583,10 +6605,10 @@
     </row>
     <row r="19" spans="1:3" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>568</v>
@@ -6594,10 +6616,10 @@
     </row>
     <row r="20" spans="1:3" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>569</v>
@@ -6605,10 +6627,10 @@
     </row>
     <row r="21" spans="1:3" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>570</v>
@@ -6616,10 +6638,10 @@
     </row>
     <row r="22" spans="1:3" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>571</v>
@@ -6627,10 +6649,10 @@
     </row>
     <row r="23" spans="1:3" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>572</v>
@@ -6638,10 +6660,10 @@
     </row>
     <row r="24" spans="1:3" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>573</v>
@@ -6649,10 +6671,10 @@
     </row>
     <row r="25" spans="1:3" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>574</v>
@@ -6660,10 +6682,10 @@
     </row>
     <row r="26" spans="1:3" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>575</v>
@@ -6671,10 +6693,10 @@
     </row>
     <row r="27" spans="1:3" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>576</v>
@@ -6682,10 +6704,10 @@
     </row>
     <row r="28" spans="1:3" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>577</v>
@@ -6693,10 +6715,10 @@
     </row>
     <row r="29" spans="1:3" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>578</v>
@@ -6704,10 +6726,10 @@
     </row>
     <row r="30" spans="1:3" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>579</v>
@@ -6715,10 +6737,10 @@
     </row>
     <row r="31" spans="1:3" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>580</v>
@@ -6726,10 +6748,10 @@
     </row>
     <row r="32" spans="1:3" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>581</v>
@@ -6737,10 +6759,10 @@
     </row>
     <row r="33" spans="1:3" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>582</v>
@@ -6748,10 +6770,10 @@
     </row>
     <row r="34" spans="1:3" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>583</v>
@@ -6759,10 +6781,10 @@
     </row>
     <row r="35" spans="1:3" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>584</v>
@@ -6770,10 +6792,10 @@
     </row>
     <row r="36" spans="1:3" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>585</v>
@@ -6781,10 +6803,10 @@
     </row>
     <row r="37" spans="1:3" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>586</v>
@@ -6792,10 +6814,10 @@
     </row>
     <row r="38" spans="1:3" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>587</v>
@@ -6803,10 +6825,10 @@
     </row>
     <row r="39" spans="1:3" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>588</v>
@@ -6814,10 +6836,10 @@
     </row>
     <row r="40" spans="1:3" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>589</v>
@@ -6825,10 +6847,10 @@
     </row>
     <row r="41" spans="1:3" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>590</v>
@@ -6836,17 +6858,28 @@
     </row>
     <row r="42" spans="1:3" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>591</v>
       </c>
     </row>
+    <row r="43" spans="1:3" ht="34" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:C42"/>
+  <autoFilter ref="A3:C43"/>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
@@ -6865,7 +6898,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -6879,186 +6912,186 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -7081,7 +7114,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -7095,242 +7128,242 @@
     </row>
     <row r="4" spans="1:2" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -7344,7 +7377,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -7357,7 +7390,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>934</v>
+        <v>947</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7371,42 +7404,42 @@
         <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="34" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G4" s="3">
         <v>25498039</v>
@@ -7414,22 +7447,22 @@
     </row>
     <row r="5" spans="1:7" ht="34" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G5" s="4">
         <v>54288508</v>
@@ -7437,22 +7470,22 @@
     </row>
     <row r="6" spans="1:7" ht="34" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G6" s="3">
         <v>43443363</v>
@@ -7460,22 +7493,22 @@
     </row>
     <row r="7" spans="1:7" ht="34" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G7" s="4">
         <v>25498039</v>
@@ -7483,22 +7516,22 @@
     </row>
     <row r="8" spans="1:7" ht="34" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G8" s="3">
         <v>1671168</v>
@@ -7506,22 +7539,22 @@
     </row>
     <row r="9" spans="1:7" ht="34" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G9" s="4">
         <v>1970176</v>
@@ -7529,22 +7562,22 @@
     </row>
     <row r="10" spans="1:7" ht="34" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G10" s="3">
         <v>18419712</v>
@@ -7552,22 +7585,22 @@
     </row>
     <row r="11" spans="1:7" ht="34" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G11" s="4">
         <v>26136576</v>
@@ -7575,22 +7608,22 @@
     </row>
     <row r="12" spans="1:7" ht="34" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G12" s="3">
         <v>7745077</v>
@@ -7598,22 +7631,22 @@
     </row>
     <row r="13" spans="1:7" ht="34" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G13" s="4">
         <v>503</v>
@@ -7621,22 +7654,22 @@
     </row>
     <row r="14" spans="1:7" ht="34" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G14" s="3">
         <v>5241</v>
@@ -7644,22 +7677,22 @@
     </row>
     <row r="15" spans="1:7" ht="34" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G15" s="4">
         <v>16899</v>
@@ -7667,22 +7700,22 @@
     </row>
     <row r="16" spans="1:7" ht="34" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G16" s="3">
         <v>279475</v>
@@ -7690,22 +7723,22 @@
     </row>
     <row r="17" spans="1:7" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G17" s="4">
         <v>9488487</v>
@@ -7713,22 +7746,22 @@
     </row>
     <row r="18" spans="1:7" ht="34" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G18" s="3">
         <v>11068</v>
@@ -7736,22 +7769,22 @@
     </row>
     <row r="19" spans="1:7" ht="34" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G19" s="4">
         <v>14503</v>
@@ -7759,22 +7792,22 @@
     </row>
     <row r="20" spans="1:7" ht="34" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G20" s="3">
         <v>11601</v>
@@ -7782,22 +7815,22 @@
     </row>
     <row r="21" spans="1:7" ht="34" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G21" s="4">
         <v>921600</v>
@@ -7805,22 +7838,22 @@
     </row>
     <row r="22" spans="1:7" ht="34" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G22" s="3">
         <v>4329472</v>
@@ -7828,64 +7861,64 @@
     </row>
     <row r="23" spans="1:7" ht="34" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="34" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="G24" s="3"/>
     </row>
     <row r="25" spans="1:7" ht="34" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G25" s="4">
         <v>5040</v>
@@ -7893,22 +7926,22 @@
     </row>
     <row r="26" spans="1:7" ht="34" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G26" s="3">
         <v>1213</v>
@@ -7916,22 +7949,22 @@
     </row>
     <row r="27" spans="1:7" ht="34" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G27" s="4">
         <v>932</v>
@@ -7939,22 +7972,22 @@
     </row>
     <row r="28" spans="1:7" ht="34" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G28" s="3">
         <v>1069056</v>
@@ -7962,22 +7995,22 @@
     </row>
     <row r="29" spans="1:7" ht="34" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G29" s="4">
         <v>187087</v>
@@ -7985,22 +8018,22 @@
     </row>
     <row r="30" spans="1:7" ht="34" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G30" s="3">
         <v>49996766</v>
@@ -8008,22 +8041,22 @@
     </row>
     <row r="31" spans="1:7" ht="34" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G31" s="4">
         <v>47656187</v>
@@ -8031,1018 +8064,1110 @@
     </row>
     <row r="32" spans="1:7" ht="34" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>134</v>
+        <v>863</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G32" s="3">
-        <v>7427833</v>
+        <v>55194314</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="34" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>854</v>
+        <v>124</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G33" s="4">
-        <v>226715</v>
+        <v>13168640</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="34" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>854</v>
+        <v>124</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G34" s="3">
-        <v>3123</v>
+        <v>4912616</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="34" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>854</v>
+        <v>124</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G35" s="4">
-        <v>1162</v>
+        <v>22573209</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="34" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>855</v>
+        <v>134</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G36" s="3">
-        <v>223269</v>
+        <v>7427833</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="34" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G37" s="4">
-        <v>213318</v>
+        <v>221657</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="34" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G38" s="3">
-        <v>435794</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="34" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G39" s="4">
-        <v>814048</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="34" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G40" s="3">
-        <v>816589</v>
+        <v>220496</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="34" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G41" s="4">
-        <v>1630308</v>
+        <v>212178</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="34" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>124</v>
+        <v>864</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G42" s="3">
-        <v>1584576</v>
+        <v>431946</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="34" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>124</v>
+        <v>865</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G43" s="4">
-        <v>1544916</v>
+        <v>1332103</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="34" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>124</v>
+        <v>865</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G44" s="3">
-        <v>3129025</v>
+        <v>1318145</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="34" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>124</v>
+        <v>865</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G45" s="4">
-        <v>24490252</v>
+        <v>2649894</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="34" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>124</v>
+        <v>865</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G46" s="3">
-        <v>741</v>
+        <v>1299493</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="34" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>124</v>
+        <v>865</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G47" s="4">
-        <v>659</v>
+        <v>1285863</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="34" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>124</v>
+        <v>865</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G48" s="3">
-        <v>17707008</v>
+        <v>2585002</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="34" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G49" s="4">
-        <v>490620</v>
+        <v>3588433</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="34" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G50" s="3">
-        <v>502297</v>
+        <v>3685328</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="34" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G51" s="4">
-        <v>992554</v>
+        <v>7273269</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="34" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G52" s="3">
-        <v>20082688</v>
+        <v>48351823</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="34" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G53" s="4">
-        <v>20459520</v>
+        <v>843</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="34" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>857</v>
+        <v>125</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G54" s="3">
-        <v>1725265</v>
+        <v>767</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="34" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>857</v>
+        <v>125</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G55" s="4">
-        <v>620</v>
+        <v>18964480</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>857</v>
+        <v>128</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G56" s="3">
-        <v>23285760</v>
+        <v>795398</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="34" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>858</v>
+        <v>128</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G57" s="4">
-        <v>1013075</v>
+        <v>845645</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="34" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>858</v>
+        <v>128</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G58" s="3">
-        <v>817454</v>
+        <v>1640680</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="34" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>858</v>
+        <v>128</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G59" s="4">
-        <v>1021573</v>
+        <v>21585920</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="34" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>858</v>
+        <v>128</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G60" s="3">
-        <v>826169</v>
+        <v>21999616</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="34" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>917</v>
+        <v>926</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G61" s="4">
-        <v>874744</v>
+        <v>2817582</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="34" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G62" s="3">
-        <v>793852</v>
+        <v>706</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="34" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G63" s="4">
-        <v>1307</v>
+        <v>25288704</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="34" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>136</v>
+        <v>867</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G64" s="3">
-        <v>23749</v>
+        <v>1138208</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="34" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>134</v>
+        <v>867</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G65" s="4">
-        <v>6348715</v>
+        <v>912685</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="34" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>138</v>
+        <v>867</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>922</v>
+        <v>931</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G66" s="3">
-        <v>779051</v>
+        <v>1167410</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="34" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>138</v>
+        <v>867</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G67" s="4">
-        <v>106524</v>
+        <v>917474</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="34" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>138</v>
+        <v>867</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G68" s="3">
-        <v>108069</v>
+        <v>980808</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="34" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>138</v>
+        <v>867</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G69" s="4">
-        <v>231</v>
+        <v>900128</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="34" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>130</v>
+        <v>867</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>926</v>
+        <v>935</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G70" s="3">
-        <v>2172</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="34" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G71" s="4">
-        <v>591</v>
+        <v>23749</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="34" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>928</v>
+        <v>937</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G72" s="3">
-        <v>13621</v>
+        <v>6348715</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="34" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G73" s="4">
-        <v>127</v>
+        <v>24640622</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="34" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>859</v>
+        <v>138</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G74" s="3">
-        <v>28580</v>
+        <v>2002187</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="34" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>859</v>
+        <v>138</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="G75" s="4">
-        <v>80203</v>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="34" customHeight="1">
+      <c r="A76" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="34" customHeight="1">
+      <c r="A77" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="G77" s="4">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="34" customHeight="1">
+      <c r="A78" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="G78" s="3">
+        <v>32860</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="34" customHeight="1">
+      <c r="A79" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="G79" s="4">
+        <v>97345</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G75"/>
+  <autoFilter ref="A3:G79"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/outputs/metadados_piloto.xlsx
+++ b/outputs/metadados_piloto.xlsx
@@ -70,7 +70,7 @@
     <t>Piloto computacional de mobilidade urbana, diferenciação socioespacial e entropia socioeconômica de trajetórias</t>
   </si>
   <si>
-    <t>2026-09-28T13:51:19.688133+00:00</t>
+    <t>2026-09-28T14:39:24.335304+00:00</t>
   </si>
   <si>
     <t>português</t>
@@ -1801,7 +1801,7 @@
     <t>Procura primeiro correspondência em segmentos com suporte da rede car e aplica uma segunda etapa na rede física completa aos trechos GTFS ainda não associados</t>
   </si>
   <si>
-    <t>Integra todos os trechos físicos GTFS válidos à camada comum e cria analysis_segment_id exclusivos para trechos que não possuem correspondência segura nas redes OSM</t>
+    <t>Integra todos os trechos físicos GTFS válidos à camada comum e cria analysis_segment_id exclusivos para trechos que não possuem correspondência segura nas redes OSM, sem interpretar automaticamente essa exclusividade como infraestrutura física exclusiva de ônibus</t>
   </si>
   <si>
     <t>Seleciona projeções sucessivas das paradas ao longo do shape quando as posições processadas estão ausentes, iguais ou decrescentes, preservando a ordem do deslocamento</t>
@@ -2131,7 +2131,7 @@
     <t>Exclui distância roteada acima da cerca externa ou circuity acima da cerca externa quando a rota também está acima do terceiro quartil, evitando excluir viagens curtas apenas por apresentarem razão elevada</t>
   </si>
   <si>
-    <t>Preserva a trajetória do agente ao criar um analysis_segment_id exclusivo para trechos físicos GTFS válidos que não possuem correspondência segura nas redes OSM</t>
+    <t>Preserva a trajetória do agente ao criar um analysis_segment_id exclusivo para trechos físicos GTFS válidos que não possuem correspondência segura nas redes OSM; a causa pode ser infraestrutura dedicada, diferença de cobertura OSM ou desacordo geométrico entre as fontes</t>
   </si>
   <si>
     <t>Metadados do piloto — Métodos de limpeza</t>
@@ -8611,7 +8611,7 @@
         <v>946</v>
       </c>
       <c r="G55" s="4">
-        <v>18964480</v>
+        <v>18960384</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="34" customHeight="1">
@@ -8703,7 +8703,7 @@
         <v>946</v>
       </c>
       <c r="G59" s="4">
-        <v>21585920</v>
+        <v>21581824</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="34" customHeight="1">
@@ -8726,7 +8726,7 @@
         <v>946</v>
       </c>
       <c r="G60" s="3">
-        <v>21999616</v>
+        <v>21995520</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="34" customHeight="1">
@@ -8795,7 +8795,7 @@
         <v>946</v>
       </c>
       <c r="G63" s="4">
-        <v>25288704</v>
+        <v>25284608</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="34" customHeight="1">
@@ -8818,7 +8818,7 @@
         <v>946</v>
       </c>
       <c r="G64" s="3">
-        <v>1138208</v>
+        <v>1138199</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="34" customHeight="1">
@@ -8841,7 +8841,7 @@
         <v>946</v>
       </c>
       <c r="G65" s="4">
-        <v>912685</v>
+        <v>912675</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="34" customHeight="1">
@@ -8864,7 +8864,7 @@
         <v>946</v>
       </c>
       <c r="G66" s="3">
-        <v>1167410</v>
+        <v>1167401</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="34" customHeight="1">
@@ -8887,7 +8887,7 @@
         <v>946</v>
       </c>
       <c r="G67" s="4">
-        <v>917474</v>
+        <v>917457</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="34" customHeight="1">
@@ -8910,7 +8910,7 @@
         <v>946</v>
       </c>
       <c r="G68" s="3">
-        <v>980808</v>
+        <v>980789</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="34" customHeight="1">
@@ -8933,7 +8933,7 @@
         <v>946</v>
       </c>
       <c r="G69" s="4">
-        <v>900128</v>
+        <v>900122</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="34" customHeight="1">
@@ -9140,7 +9140,7 @@
         <v>946</v>
       </c>
       <c r="G78" s="3">
-        <v>32860</v>
+        <v>32875</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="34" customHeight="1">
@@ -9163,7 +9163,7 @@
         <v>946</v>
       </c>
       <c r="G79" s="4">
-        <v>97345</v>
+        <v>97381</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metadados_piloto.xlsx
+++ b/outputs/metadados_piloto.xlsx
@@ -70,7 +70,7 @@
     <t>Piloto computacional de mobilidade urbana, diferenciação socioespacial e entropia socioeconômica de trajetórias</t>
   </si>
   <si>
-    <t>2026-09-28T14:39:24.335304+00:00</t>
+    <t>2026-09-28T15:26:26.033147+00:00</t>
   </si>
   <si>
     <t>português</t>
@@ -9140,7 +9140,7 @@
         <v>946</v>
       </c>
       <c r="G78" s="3">
-        <v>32875</v>
+        <v>32959</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="34" customHeight="1">
@@ -9163,7 +9163,7 @@
         <v>946</v>
       </c>
       <c r="G79" s="4">
-        <v>97381</v>
+        <v>97594</v>
       </c>
     </row>
   </sheetData>
